--- a/Assets/Excel/Pets.xlsx
+++ b/Assets/Excel/Pets.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC8AF79-0BF8-4DFF-A564-AFE9CFCB108C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72358E0-EE27-4BDA-B715-F183289E5B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="1" r:id="rId2"/>
+    <sheet name="Pets" sheetId="2" r:id="rId1"/>
+    <sheet name="PetLevelup" sheetId="3" r:id="rId2"/>
+    <sheet name="TalentSkillNum" sheetId="4" r:id="rId3"/>
+    <sheet name="TalentSkill" sheetId="5" r:id="rId4"/>
+    <sheet name="备份" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="114">
   <si>
     <t>String</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -263,13 +266,193 @@
   </si>
   <si>
     <t>Pet_103</t>
+  </si>
+  <si>
+    <t>等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FoodCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击百分比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DefenceRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御百分比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命百分比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从本级升到下一级的消耗饲料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物品质</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rarity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PetRarity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天赋技能数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TalentSkillNum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stirng</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DefenceRate</t>
+  </si>
+  <si>
+    <t>HpRate</t>
+  </si>
+  <si>
+    <t>天赋技能池属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>品质1权重</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>品质1数值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>品质1数值成长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rarity1Weight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rarity1Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rarity1Delta</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>品质2权重</t>
+  </si>
+  <si>
+    <t>品质2数值</t>
+  </si>
+  <si>
+    <t>品质2数值成长</t>
+  </si>
+  <si>
+    <t>品质3权重</t>
+  </si>
+  <si>
+    <t>品质3数值</t>
+  </si>
+  <si>
+    <t>品质3数值成长</t>
+  </si>
+  <si>
+    <t>品质4权重</t>
+  </si>
+  <si>
+    <t>品质4数值</t>
+  </si>
+  <si>
+    <t>品质4数值成长</t>
+  </si>
+  <si>
+    <t>Rarity2Weight</t>
+  </si>
+  <si>
+    <t>Rarity2Value</t>
+  </si>
+  <si>
+    <t>Rarity2Delta</t>
+  </si>
+  <si>
+    <t>Rarity3Weight</t>
+  </si>
+  <si>
+    <t>Rarity3Value</t>
+  </si>
+  <si>
+    <t>Rarity3Delta</t>
+  </si>
+  <si>
+    <t>Rarity4Weight</t>
+  </si>
+  <si>
+    <t>Rarity4Value</t>
+  </si>
+  <si>
+    <t>Rarity4Delta</t>
+  </si>
+  <si>
+    <t>该类型属性权重</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttrWeight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天赋技能最高等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TalentSkillMaxLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AbsorbLimit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最多吞噬次数(最大星级）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,6 +480,14 @@
       <sz val="11"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -337,7 +528,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -360,6 +551,20 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -640,172 +845,181 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E113BB45-2004-4A47-8070-A66C92D5B66E}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="9.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="94.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.75" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="2" max="3" width="10.75" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.75" style="2" customWidth="1"/>
+    <col min="13" max="13" width="10.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>101</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>3</v>
+      <c r="C4" s="2">
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="F4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
         <v>5</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <v>350</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
@@ -822,86 +1036,95 @@
       <c r="M4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>102</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="2">
         <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="2">
-        <v>2</v>
-      </c>
       <c r="G5" s="2">
+        <v>2</v>
+      </c>
+      <c r="H5" s="2">
         <v>0</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>137</v>
       </c>
-      <c r="I5" s="2">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K5" s="2">
+      <c r="L5" s="2">
         <v>15</v>
       </c>
-      <c r="L5" s="2">
-        <v>1</v>
-      </c>
       <c r="M5" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>103</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
       <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
         <v>108</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <v>0</v>
       </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="2">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K6" s="2">
+      <c r="L6" s="2">
         <v>10</v>
       </c>
-      <c r="L6" s="2">
+      <c r="M6" s="2">
         <v>5</v>
       </c>
-      <c r="M6" s="2">
+      <c r="N6" s="2">
         <v>999</v>
       </c>
     </row>
@@ -913,9 +1136,9 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{51EBD029-4B24-4585-92AB-5BFB4473353B}">
           <x14:formula1>
-            <xm:f>Sheet2!$B$1:$B$25</xm:f>
+            <xm:f>备份!$B$1:$B$25</xm:f>
           </x14:formula1>
-          <xm:sqref>J4:J6</xm:sqref>
+          <xm:sqref>K4:K6</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -924,6 +1147,7906 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E76EACD-2167-4635-97EC-A76DDB474FD3}">
+  <dimension ref="A1:F303"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="9.875" customWidth="1"/>
+    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="10">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10">
+        <v>1</v>
+      </c>
+      <c r="C4" s="10">
+        <v>100</v>
+      </c>
+      <c r="D4" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="11">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10">
+        <v>2</v>
+      </c>
+      <c r="C5" s="10">
+        <v>200</v>
+      </c>
+      <c r="D5" s="11">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="10">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10">
+        <v>3</v>
+      </c>
+      <c r="C6" s="10">
+        <v>300</v>
+      </c>
+      <c r="D6" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="E6" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="F6" s="11">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="10">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10">
+        <v>4</v>
+      </c>
+      <c r="C7" s="10">
+        <v>400</v>
+      </c>
+      <c r="D7" s="11">
+        <v>2</v>
+      </c>
+      <c r="E7" s="10">
+        <v>2</v>
+      </c>
+      <c r="F7" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="10">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10">
+        <v>5</v>
+      </c>
+      <c r="C8" s="10">
+        <v>500</v>
+      </c>
+      <c r="D8" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="E8" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F8" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="10">
+        <v>1</v>
+      </c>
+      <c r="B9" s="10">
+        <v>6</v>
+      </c>
+      <c r="C9" s="10">
+        <v>600</v>
+      </c>
+      <c r="D9" s="11">
+        <v>3</v>
+      </c>
+      <c r="E9" s="10">
+        <v>3</v>
+      </c>
+      <c r="F9" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="10">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10">
+        <v>7</v>
+      </c>
+      <c r="C10" s="10">
+        <v>700</v>
+      </c>
+      <c r="D10" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="E10" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="F10" s="11">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="10">
+        <v>1</v>
+      </c>
+      <c r="B11" s="10">
+        <v>8</v>
+      </c>
+      <c r="C11" s="10">
+        <v>800</v>
+      </c>
+      <c r="D11" s="11">
+        <v>4</v>
+      </c>
+      <c r="E11" s="10">
+        <v>4</v>
+      </c>
+      <c r="F11" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="10">
+        <v>1</v>
+      </c>
+      <c r="B12" s="10">
+        <v>9</v>
+      </c>
+      <c r="C12" s="10">
+        <v>900</v>
+      </c>
+      <c r="D12" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="E12" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="F12" s="11">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="10">
+        <v>1</v>
+      </c>
+      <c r="B13" s="10">
+        <v>10</v>
+      </c>
+      <c r="C13" s="10">
+        <v>1000</v>
+      </c>
+      <c r="D13" s="11">
+        <v>5</v>
+      </c>
+      <c r="E13" s="10">
+        <v>5</v>
+      </c>
+      <c r="F13" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="10">
+        <v>1</v>
+      </c>
+      <c r="B14" s="10">
+        <v>11</v>
+      </c>
+      <c r="C14" s="10">
+        <v>1100</v>
+      </c>
+      <c r="D14" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="E14" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="F14" s="11">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="10">
+        <v>1</v>
+      </c>
+      <c r="B15" s="10">
+        <v>12</v>
+      </c>
+      <c r="C15" s="10">
+        <v>1200</v>
+      </c>
+      <c r="D15" s="11">
+        <v>6</v>
+      </c>
+      <c r="E15" s="10">
+        <v>6</v>
+      </c>
+      <c r="F15" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="10">
+        <v>1</v>
+      </c>
+      <c r="B16" s="10">
+        <v>13</v>
+      </c>
+      <c r="C16" s="10">
+        <v>1300</v>
+      </c>
+      <c r="D16" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="E16" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="F16" s="11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="10">
+        <v>1</v>
+      </c>
+      <c r="B17" s="10">
+        <v>14</v>
+      </c>
+      <c r="C17" s="10">
+        <v>1400</v>
+      </c>
+      <c r="D17" s="11">
+        <v>7</v>
+      </c>
+      <c r="E17" s="10">
+        <v>7</v>
+      </c>
+      <c r="F17" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="10">
+        <v>1</v>
+      </c>
+      <c r="B18" s="10">
+        <v>15</v>
+      </c>
+      <c r="C18" s="10">
+        <v>1500</v>
+      </c>
+      <c r="D18" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="E18" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="F18" s="11">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="10">
+        <v>1</v>
+      </c>
+      <c r="B19" s="10">
+        <v>16</v>
+      </c>
+      <c r="C19" s="10">
+        <v>1600</v>
+      </c>
+      <c r="D19" s="11">
+        <v>8</v>
+      </c>
+      <c r="E19" s="10">
+        <v>8</v>
+      </c>
+      <c r="F19" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="10">
+        <v>1</v>
+      </c>
+      <c r="B20" s="10">
+        <v>17</v>
+      </c>
+      <c r="C20" s="10">
+        <v>1700</v>
+      </c>
+      <c r="D20" s="11">
+        <v>8.5</v>
+      </c>
+      <c r="E20" s="11">
+        <v>8.5</v>
+      </c>
+      <c r="F20" s="11">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="10">
+        <v>1</v>
+      </c>
+      <c r="B21" s="10">
+        <v>18</v>
+      </c>
+      <c r="C21" s="10">
+        <v>1800</v>
+      </c>
+      <c r="D21" s="11">
+        <v>9</v>
+      </c>
+      <c r="E21" s="10">
+        <v>9</v>
+      </c>
+      <c r="F21" s="10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="10">
+        <v>1</v>
+      </c>
+      <c r="B22" s="10">
+        <v>19</v>
+      </c>
+      <c r="C22" s="10">
+        <v>1900</v>
+      </c>
+      <c r="D22" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="E22" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="F22" s="11">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="10">
+        <v>1</v>
+      </c>
+      <c r="B23" s="10">
+        <v>20</v>
+      </c>
+      <c r="C23" s="10">
+        <v>2000</v>
+      </c>
+      <c r="D23" s="11">
+        <v>10</v>
+      </c>
+      <c r="E23" s="10">
+        <v>10</v>
+      </c>
+      <c r="F23" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="10">
+        <v>1</v>
+      </c>
+      <c r="B24" s="10">
+        <v>21</v>
+      </c>
+      <c r="C24" s="10">
+        <v>2100</v>
+      </c>
+      <c r="D24" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="E24" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="F24" s="11">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="10">
+        <v>1</v>
+      </c>
+      <c r="B25" s="10">
+        <v>22</v>
+      </c>
+      <c r="C25" s="10">
+        <v>2200</v>
+      </c>
+      <c r="D25" s="11">
+        <v>11</v>
+      </c>
+      <c r="E25" s="10">
+        <v>11</v>
+      </c>
+      <c r="F25" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="10">
+        <v>1</v>
+      </c>
+      <c r="B26" s="10">
+        <v>23</v>
+      </c>
+      <c r="C26" s="10">
+        <v>2300</v>
+      </c>
+      <c r="D26" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="E26" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="F26" s="11">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="10">
+        <v>1</v>
+      </c>
+      <c r="B27" s="10">
+        <v>24</v>
+      </c>
+      <c r="C27" s="10">
+        <v>2400</v>
+      </c>
+      <c r="D27" s="11">
+        <v>12</v>
+      </c>
+      <c r="E27" s="10">
+        <v>12</v>
+      </c>
+      <c r="F27" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="10">
+        <v>1</v>
+      </c>
+      <c r="B28" s="10">
+        <v>25</v>
+      </c>
+      <c r="C28" s="10">
+        <v>2500</v>
+      </c>
+      <c r="D28" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="E28" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="F28" s="11">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>1</v>
+      </c>
+      <c r="B29" s="10">
+        <v>26</v>
+      </c>
+      <c r="C29" s="10">
+        <v>2600</v>
+      </c>
+      <c r="D29" s="11">
+        <v>13</v>
+      </c>
+      <c r="E29" s="10">
+        <v>13</v>
+      </c>
+      <c r="F29" s="10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>1</v>
+      </c>
+      <c r="B30" s="10">
+        <v>27</v>
+      </c>
+      <c r="C30" s="10">
+        <v>2700</v>
+      </c>
+      <c r="D30" s="11">
+        <v>13.5</v>
+      </c>
+      <c r="E30" s="11">
+        <v>13.5</v>
+      </c>
+      <c r="F30" s="11">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>1</v>
+      </c>
+      <c r="B31" s="10">
+        <v>28</v>
+      </c>
+      <c r="C31" s="10">
+        <v>2800</v>
+      </c>
+      <c r="D31" s="11">
+        <v>14</v>
+      </c>
+      <c r="E31" s="10">
+        <v>14</v>
+      </c>
+      <c r="F31" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>1</v>
+      </c>
+      <c r="B32" s="10">
+        <v>29</v>
+      </c>
+      <c r="C32" s="10">
+        <v>2900</v>
+      </c>
+      <c r="D32" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="E32" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="F32" s="11">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>1</v>
+      </c>
+      <c r="B33" s="10">
+        <v>30</v>
+      </c>
+      <c r="C33" s="10">
+        <v>3000</v>
+      </c>
+      <c r="D33" s="11">
+        <v>15</v>
+      </c>
+      <c r="E33" s="10">
+        <v>15</v>
+      </c>
+      <c r="F33" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>1</v>
+      </c>
+      <c r="B34" s="10">
+        <v>31</v>
+      </c>
+      <c r="C34" s="10">
+        <v>3100</v>
+      </c>
+      <c r="D34" s="11">
+        <v>15.5</v>
+      </c>
+      <c r="E34" s="11">
+        <v>15.5</v>
+      </c>
+      <c r="F34" s="11">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>1</v>
+      </c>
+      <c r="B35" s="10">
+        <v>32</v>
+      </c>
+      <c r="C35" s="10">
+        <v>3200</v>
+      </c>
+      <c r="D35" s="11">
+        <v>16</v>
+      </c>
+      <c r="E35" s="10">
+        <v>16</v>
+      </c>
+      <c r="F35" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>1</v>
+      </c>
+      <c r="B36" s="10">
+        <v>33</v>
+      </c>
+      <c r="C36" s="10">
+        <v>3300</v>
+      </c>
+      <c r="D36" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="E36" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="F36" s="11">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>1</v>
+      </c>
+      <c r="B37" s="10">
+        <v>34</v>
+      </c>
+      <c r="C37" s="10">
+        <v>3400</v>
+      </c>
+      <c r="D37" s="11">
+        <v>17</v>
+      </c>
+      <c r="E37" s="10">
+        <v>17</v>
+      </c>
+      <c r="F37" s="10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>1</v>
+      </c>
+      <c r="B38" s="10">
+        <v>35</v>
+      </c>
+      <c r="C38" s="10">
+        <v>3500</v>
+      </c>
+      <c r="D38" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="E38" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="F38" s="11">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>1</v>
+      </c>
+      <c r="B39" s="10">
+        <v>36</v>
+      </c>
+      <c r="C39" s="10">
+        <v>3600</v>
+      </c>
+      <c r="D39" s="11">
+        <v>18</v>
+      </c>
+      <c r="E39" s="10">
+        <v>18</v>
+      </c>
+      <c r="F39" s="10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="10">
+        <v>1</v>
+      </c>
+      <c r="B40" s="10">
+        <v>37</v>
+      </c>
+      <c r="C40" s="10">
+        <v>3700</v>
+      </c>
+      <c r="D40" s="11">
+        <v>18.5</v>
+      </c>
+      <c r="E40" s="11">
+        <v>18.5</v>
+      </c>
+      <c r="F40" s="11">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="10">
+        <v>1</v>
+      </c>
+      <c r="B41" s="10">
+        <v>38</v>
+      </c>
+      <c r="C41" s="10">
+        <v>3800</v>
+      </c>
+      <c r="D41" s="11">
+        <v>19</v>
+      </c>
+      <c r="E41" s="10">
+        <v>19</v>
+      </c>
+      <c r="F41" s="10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" s="10">
+        <v>1</v>
+      </c>
+      <c r="B42" s="10">
+        <v>39</v>
+      </c>
+      <c r="C42" s="10">
+        <v>3900</v>
+      </c>
+      <c r="D42" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="E42" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="F42" s="11">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" s="10">
+        <v>1</v>
+      </c>
+      <c r="B43" s="10">
+        <v>40</v>
+      </c>
+      <c r="C43" s="10">
+        <v>4000</v>
+      </c>
+      <c r="D43" s="11">
+        <v>20</v>
+      </c>
+      <c r="E43" s="10">
+        <v>20</v>
+      </c>
+      <c r="F43" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" s="10">
+        <v>1</v>
+      </c>
+      <c r="B44" s="10">
+        <v>41</v>
+      </c>
+      <c r="C44" s="10">
+        <v>4100</v>
+      </c>
+      <c r="D44" s="11">
+        <v>20.5</v>
+      </c>
+      <c r="E44" s="11">
+        <v>20.5</v>
+      </c>
+      <c r="F44" s="11">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="10">
+        <v>1</v>
+      </c>
+      <c r="B45" s="10">
+        <v>42</v>
+      </c>
+      <c r="C45" s="10">
+        <v>4200</v>
+      </c>
+      <c r="D45" s="11">
+        <v>21</v>
+      </c>
+      <c r="E45" s="10">
+        <v>21</v>
+      </c>
+      <c r="F45" s="10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="10">
+        <v>1</v>
+      </c>
+      <c r="B46" s="10">
+        <v>43</v>
+      </c>
+      <c r="C46" s="10">
+        <v>4300</v>
+      </c>
+      <c r="D46" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="E46" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="F46" s="11">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="10">
+        <v>1</v>
+      </c>
+      <c r="B47" s="10">
+        <v>44</v>
+      </c>
+      <c r="C47" s="10">
+        <v>4400</v>
+      </c>
+      <c r="D47" s="11">
+        <v>22</v>
+      </c>
+      <c r="E47" s="10">
+        <v>22</v>
+      </c>
+      <c r="F47" s="10">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" s="10">
+        <v>1</v>
+      </c>
+      <c r="B48" s="10">
+        <v>45</v>
+      </c>
+      <c r="C48" s="10">
+        <v>4500</v>
+      </c>
+      <c r="D48" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="E48" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="F48" s="11">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" s="10">
+        <v>1</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46</v>
+      </c>
+      <c r="C49" s="10">
+        <v>4600</v>
+      </c>
+      <c r="D49" s="11">
+        <v>23</v>
+      </c>
+      <c r="E49" s="10">
+        <v>23</v>
+      </c>
+      <c r="F49" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" s="10">
+        <v>1</v>
+      </c>
+      <c r="B50" s="10">
+        <v>47</v>
+      </c>
+      <c r="C50" s="10">
+        <v>4700</v>
+      </c>
+      <c r="D50" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="E50" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="F50" s="11">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="10">
+        <v>1</v>
+      </c>
+      <c r="B51" s="10">
+        <v>48</v>
+      </c>
+      <c r="C51" s="10">
+        <v>4800</v>
+      </c>
+      <c r="D51" s="11">
+        <v>24</v>
+      </c>
+      <c r="E51" s="10">
+        <v>24</v>
+      </c>
+      <c r="F51" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" s="10">
+        <v>1</v>
+      </c>
+      <c r="B52" s="10">
+        <v>49</v>
+      </c>
+      <c r="C52" s="10">
+        <v>4900</v>
+      </c>
+      <c r="D52" s="11">
+        <v>24.5</v>
+      </c>
+      <c r="E52" s="11">
+        <v>24.5</v>
+      </c>
+      <c r="F52" s="11">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" s="10">
+        <v>1</v>
+      </c>
+      <c r="B53" s="10">
+        <v>50</v>
+      </c>
+      <c r="C53" s="10">
+        <v>5000</v>
+      </c>
+      <c r="D53" s="11">
+        <v>25</v>
+      </c>
+      <c r="E53" s="10">
+        <v>25</v>
+      </c>
+      <c r="F53" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>1</v>
+      </c>
+      <c r="B54" s="10">
+        <v>51</v>
+      </c>
+      <c r="C54" s="10">
+        <v>5100</v>
+      </c>
+      <c r="D54" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="E54" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="F54" s="11">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>1</v>
+      </c>
+      <c r="B55" s="10">
+        <v>52</v>
+      </c>
+      <c r="C55" s="10">
+        <v>5200</v>
+      </c>
+      <c r="D55" s="11">
+        <v>26</v>
+      </c>
+      <c r="E55" s="10">
+        <v>26</v>
+      </c>
+      <c r="F55" s="10">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>1</v>
+      </c>
+      <c r="B56" s="10">
+        <v>53</v>
+      </c>
+      <c r="C56" s="10">
+        <v>5300</v>
+      </c>
+      <c r="D56" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="E56" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="F56" s="11">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>1</v>
+      </c>
+      <c r="B57" s="10">
+        <v>54</v>
+      </c>
+      <c r="C57" s="10">
+        <v>5400</v>
+      </c>
+      <c r="D57" s="11">
+        <v>27</v>
+      </c>
+      <c r="E57" s="10">
+        <v>27</v>
+      </c>
+      <c r="F57" s="10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>1</v>
+      </c>
+      <c r="B58" s="10">
+        <v>55</v>
+      </c>
+      <c r="C58" s="10">
+        <v>5500</v>
+      </c>
+      <c r="D58" s="11">
+        <v>27.5</v>
+      </c>
+      <c r="E58" s="11">
+        <v>27.5</v>
+      </c>
+      <c r="F58" s="11">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>1</v>
+      </c>
+      <c r="B59" s="10">
+        <v>56</v>
+      </c>
+      <c r="C59" s="10">
+        <v>5600</v>
+      </c>
+      <c r="D59" s="11">
+        <v>28</v>
+      </c>
+      <c r="E59" s="10">
+        <v>28</v>
+      </c>
+      <c r="F59" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>1</v>
+      </c>
+      <c r="B60" s="10">
+        <v>57</v>
+      </c>
+      <c r="C60" s="10">
+        <v>5700</v>
+      </c>
+      <c r="D60" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="E60" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="F60" s="11">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" s="10">
+        <v>1</v>
+      </c>
+      <c r="B61" s="10">
+        <v>58</v>
+      </c>
+      <c r="C61" s="10">
+        <v>5800</v>
+      </c>
+      <c r="D61" s="11">
+        <v>29</v>
+      </c>
+      <c r="E61" s="10">
+        <v>29</v>
+      </c>
+      <c r="F61" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" s="10">
+        <v>1</v>
+      </c>
+      <c r="B62" s="10">
+        <v>59</v>
+      </c>
+      <c r="C62" s="10">
+        <v>5900</v>
+      </c>
+      <c r="D62" s="11">
+        <v>29.5</v>
+      </c>
+      <c r="E62" s="11">
+        <v>29.5</v>
+      </c>
+      <c r="F62" s="11">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="10">
+        <v>1</v>
+      </c>
+      <c r="B63" s="10">
+        <v>60</v>
+      </c>
+      <c r="C63" s="10">
+        <v>6000</v>
+      </c>
+      <c r="D63" s="11">
+        <v>30</v>
+      </c>
+      <c r="E63" s="10">
+        <v>30</v>
+      </c>
+      <c r="F63" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64" s="10">
+        <v>1</v>
+      </c>
+      <c r="B64" s="10">
+        <v>61</v>
+      </c>
+      <c r="C64" s="10">
+        <v>6100</v>
+      </c>
+      <c r="D64" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="E64" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="F64" s="11">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="10">
+        <v>1</v>
+      </c>
+      <c r="B65" s="10">
+        <v>62</v>
+      </c>
+      <c r="C65" s="10">
+        <v>6200</v>
+      </c>
+      <c r="D65" s="11">
+        <v>31</v>
+      </c>
+      <c r="E65" s="10">
+        <v>31</v>
+      </c>
+      <c r="F65" s="10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="10">
+        <v>1</v>
+      </c>
+      <c r="B66" s="10">
+        <v>63</v>
+      </c>
+      <c r="C66" s="10">
+        <v>6300</v>
+      </c>
+      <c r="D66" s="11">
+        <v>31.5</v>
+      </c>
+      <c r="E66" s="11">
+        <v>31.5</v>
+      </c>
+      <c r="F66" s="11">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="10">
+        <v>1</v>
+      </c>
+      <c r="B67" s="10">
+        <v>64</v>
+      </c>
+      <c r="C67" s="10">
+        <v>6400</v>
+      </c>
+      <c r="D67" s="11">
+        <v>32</v>
+      </c>
+      <c r="E67" s="10">
+        <v>32</v>
+      </c>
+      <c r="F67" s="10">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="10">
+        <v>1</v>
+      </c>
+      <c r="B68" s="10">
+        <v>65</v>
+      </c>
+      <c r="C68" s="10">
+        <v>6500</v>
+      </c>
+      <c r="D68" s="11">
+        <v>32.5</v>
+      </c>
+      <c r="E68" s="11">
+        <v>32.5</v>
+      </c>
+      <c r="F68" s="11">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="10">
+        <v>1</v>
+      </c>
+      <c r="B69" s="10">
+        <v>66</v>
+      </c>
+      <c r="C69" s="10">
+        <v>6600</v>
+      </c>
+      <c r="D69" s="11">
+        <v>33</v>
+      </c>
+      <c r="E69" s="10">
+        <v>33</v>
+      </c>
+      <c r="F69" s="10">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="10">
+        <v>1</v>
+      </c>
+      <c r="B70" s="10">
+        <v>67</v>
+      </c>
+      <c r="C70" s="10">
+        <v>6700</v>
+      </c>
+      <c r="D70" s="11">
+        <v>33.5</v>
+      </c>
+      <c r="E70" s="11">
+        <v>33.5</v>
+      </c>
+      <c r="F70" s="11">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="10">
+        <v>1</v>
+      </c>
+      <c r="B71" s="10">
+        <v>68</v>
+      </c>
+      <c r="C71" s="10">
+        <v>6800</v>
+      </c>
+      <c r="D71" s="11">
+        <v>34</v>
+      </c>
+      <c r="E71" s="10">
+        <v>34</v>
+      </c>
+      <c r="F71" s="10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="10">
+        <v>1</v>
+      </c>
+      <c r="B72" s="10">
+        <v>69</v>
+      </c>
+      <c r="C72" s="10">
+        <v>6900</v>
+      </c>
+      <c r="D72" s="11">
+        <v>34.5</v>
+      </c>
+      <c r="E72" s="11">
+        <v>34.5</v>
+      </c>
+      <c r="F72" s="11">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="10">
+        <v>1</v>
+      </c>
+      <c r="B73" s="10">
+        <v>70</v>
+      </c>
+      <c r="C73" s="10">
+        <v>7000</v>
+      </c>
+      <c r="D73" s="11">
+        <v>35</v>
+      </c>
+      <c r="E73" s="10">
+        <v>35</v>
+      </c>
+      <c r="F73" s="10">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="10">
+        <v>1</v>
+      </c>
+      <c r="B74" s="10">
+        <v>71</v>
+      </c>
+      <c r="C74" s="10">
+        <v>7100</v>
+      </c>
+      <c r="D74" s="11">
+        <v>35.5</v>
+      </c>
+      <c r="E74" s="11">
+        <v>35.5</v>
+      </c>
+      <c r="F74" s="11">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75" s="10">
+        <v>1</v>
+      </c>
+      <c r="B75" s="10">
+        <v>72</v>
+      </c>
+      <c r="C75" s="10">
+        <v>7200</v>
+      </c>
+      <c r="D75" s="11">
+        <v>36</v>
+      </c>
+      <c r="E75" s="10">
+        <v>36</v>
+      </c>
+      <c r="F75" s="10">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A76" s="10">
+        <v>1</v>
+      </c>
+      <c r="B76" s="10">
+        <v>73</v>
+      </c>
+      <c r="C76" s="10">
+        <v>7300</v>
+      </c>
+      <c r="D76" s="11">
+        <v>36.5</v>
+      </c>
+      <c r="E76" s="11">
+        <v>36.5</v>
+      </c>
+      <c r="F76" s="11">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="10">
+        <v>1</v>
+      </c>
+      <c r="B77" s="10">
+        <v>74</v>
+      </c>
+      <c r="C77" s="10">
+        <v>7400</v>
+      </c>
+      <c r="D77" s="11">
+        <v>37</v>
+      </c>
+      <c r="E77" s="10">
+        <v>37</v>
+      </c>
+      <c r="F77" s="10">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A78" s="10">
+        <v>1</v>
+      </c>
+      <c r="B78" s="10">
+        <v>75</v>
+      </c>
+      <c r="C78" s="10">
+        <v>7500</v>
+      </c>
+      <c r="D78" s="11">
+        <v>37.5</v>
+      </c>
+      <c r="E78" s="11">
+        <v>37.5</v>
+      </c>
+      <c r="F78" s="11">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" s="10">
+        <v>1</v>
+      </c>
+      <c r="B79" s="10">
+        <v>76</v>
+      </c>
+      <c r="C79" s="10">
+        <v>7600</v>
+      </c>
+      <c r="D79" s="11">
+        <v>38</v>
+      </c>
+      <c r="E79" s="10">
+        <v>38</v>
+      </c>
+      <c r="F79" s="10">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="10">
+        <v>1</v>
+      </c>
+      <c r="B80" s="10">
+        <v>77</v>
+      </c>
+      <c r="C80" s="10">
+        <v>7700</v>
+      </c>
+      <c r="D80" s="11">
+        <v>38.5</v>
+      </c>
+      <c r="E80" s="11">
+        <v>38.5</v>
+      </c>
+      <c r="F80" s="11">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81" s="10">
+        <v>1</v>
+      </c>
+      <c r="B81" s="10">
+        <v>78</v>
+      </c>
+      <c r="C81" s="10">
+        <v>7800</v>
+      </c>
+      <c r="D81" s="11">
+        <v>39</v>
+      </c>
+      <c r="E81" s="10">
+        <v>39</v>
+      </c>
+      <c r="F81" s="10">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82" s="10">
+        <v>1</v>
+      </c>
+      <c r="B82" s="10">
+        <v>79</v>
+      </c>
+      <c r="C82" s="10">
+        <v>7900</v>
+      </c>
+      <c r="D82" s="11">
+        <v>39.5</v>
+      </c>
+      <c r="E82" s="11">
+        <v>39.5</v>
+      </c>
+      <c r="F82" s="11">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A83" s="10">
+        <v>1</v>
+      </c>
+      <c r="B83" s="10">
+        <v>80</v>
+      </c>
+      <c r="C83" s="10">
+        <v>8000</v>
+      </c>
+      <c r="D83" s="11">
+        <v>40</v>
+      </c>
+      <c r="E83" s="10">
+        <v>40</v>
+      </c>
+      <c r="F83" s="10">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A84" s="10">
+        <v>1</v>
+      </c>
+      <c r="B84" s="10">
+        <v>81</v>
+      </c>
+      <c r="C84" s="10">
+        <v>8100</v>
+      </c>
+      <c r="D84" s="11">
+        <v>40.5</v>
+      </c>
+      <c r="E84" s="11">
+        <v>40.5</v>
+      </c>
+      <c r="F84" s="11">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A85" s="10">
+        <v>1</v>
+      </c>
+      <c r="B85" s="10">
+        <v>82</v>
+      </c>
+      <c r="C85" s="10">
+        <v>8200</v>
+      </c>
+      <c r="D85" s="11">
+        <v>41</v>
+      </c>
+      <c r="E85" s="10">
+        <v>41</v>
+      </c>
+      <c r="F85" s="10">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A86" s="10">
+        <v>1</v>
+      </c>
+      <c r="B86" s="10">
+        <v>83</v>
+      </c>
+      <c r="C86" s="10">
+        <v>8300</v>
+      </c>
+      <c r="D86" s="11">
+        <v>41.5</v>
+      </c>
+      <c r="E86" s="11">
+        <v>41.5</v>
+      </c>
+      <c r="F86" s="11">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" s="10">
+        <v>1</v>
+      </c>
+      <c r="B87" s="10">
+        <v>84</v>
+      </c>
+      <c r="C87" s="10">
+        <v>8400</v>
+      </c>
+      <c r="D87" s="11">
+        <v>42</v>
+      </c>
+      <c r="E87" s="10">
+        <v>42</v>
+      </c>
+      <c r="F87" s="10">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88" s="10">
+        <v>1</v>
+      </c>
+      <c r="B88" s="10">
+        <v>85</v>
+      </c>
+      <c r="C88" s="10">
+        <v>8500</v>
+      </c>
+      <c r="D88" s="11">
+        <v>42.5</v>
+      </c>
+      <c r="E88" s="11">
+        <v>42.5</v>
+      </c>
+      <c r="F88" s="11">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89" s="10">
+        <v>1</v>
+      </c>
+      <c r="B89" s="10">
+        <v>86</v>
+      </c>
+      <c r="C89" s="10">
+        <v>8600</v>
+      </c>
+      <c r="D89" s="11">
+        <v>43</v>
+      </c>
+      <c r="E89" s="10">
+        <v>43</v>
+      </c>
+      <c r="F89" s="10">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" s="10">
+        <v>1</v>
+      </c>
+      <c r="B90" s="10">
+        <v>87</v>
+      </c>
+      <c r="C90" s="10">
+        <v>8700</v>
+      </c>
+      <c r="D90" s="11">
+        <v>43.5</v>
+      </c>
+      <c r="E90" s="11">
+        <v>43.5</v>
+      </c>
+      <c r="F90" s="11">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A91" s="10">
+        <v>1</v>
+      </c>
+      <c r="B91" s="10">
+        <v>88</v>
+      </c>
+      <c r="C91" s="10">
+        <v>8800</v>
+      </c>
+      <c r="D91" s="11">
+        <v>44</v>
+      </c>
+      <c r="E91" s="10">
+        <v>44</v>
+      </c>
+      <c r="F91" s="10">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92" s="10">
+        <v>1</v>
+      </c>
+      <c r="B92" s="10">
+        <v>89</v>
+      </c>
+      <c r="C92" s="10">
+        <v>8900</v>
+      </c>
+      <c r="D92" s="11">
+        <v>44.5</v>
+      </c>
+      <c r="E92" s="11">
+        <v>44.5</v>
+      </c>
+      <c r="F92" s="11">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A93" s="10">
+        <v>1</v>
+      </c>
+      <c r="B93" s="10">
+        <v>90</v>
+      </c>
+      <c r="C93" s="10">
+        <v>9000</v>
+      </c>
+      <c r="D93" s="11">
+        <v>45</v>
+      </c>
+      <c r="E93" s="10">
+        <v>45</v>
+      </c>
+      <c r="F93" s="10">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A94" s="10">
+        <v>1</v>
+      </c>
+      <c r="B94" s="10">
+        <v>91</v>
+      </c>
+      <c r="C94" s="10">
+        <v>9100</v>
+      </c>
+      <c r="D94" s="11">
+        <v>45.5</v>
+      </c>
+      <c r="E94" s="11">
+        <v>45.5</v>
+      </c>
+      <c r="F94" s="11">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A95" s="10">
+        <v>1</v>
+      </c>
+      <c r="B95" s="10">
+        <v>92</v>
+      </c>
+      <c r="C95" s="10">
+        <v>9200</v>
+      </c>
+      <c r="D95" s="11">
+        <v>46</v>
+      </c>
+      <c r="E95" s="10">
+        <v>46</v>
+      </c>
+      <c r="F95" s="10">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96" s="10">
+        <v>1</v>
+      </c>
+      <c r="B96" s="10">
+        <v>93</v>
+      </c>
+      <c r="C96" s="10">
+        <v>9300</v>
+      </c>
+      <c r="D96" s="11">
+        <v>46.5</v>
+      </c>
+      <c r="E96" s="11">
+        <v>46.5</v>
+      </c>
+      <c r="F96" s="11">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97" s="10">
+        <v>1</v>
+      </c>
+      <c r="B97" s="10">
+        <v>94</v>
+      </c>
+      <c r="C97" s="10">
+        <v>9400</v>
+      </c>
+      <c r="D97" s="11">
+        <v>47</v>
+      </c>
+      <c r="E97" s="10">
+        <v>47</v>
+      </c>
+      <c r="F97" s="10">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98" s="10">
+        <v>1</v>
+      </c>
+      <c r="B98" s="10">
+        <v>95</v>
+      </c>
+      <c r="C98" s="10">
+        <v>9500</v>
+      </c>
+      <c r="D98" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="E98" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="F98" s="11">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A99" s="10">
+        <v>1</v>
+      </c>
+      <c r="B99" s="10">
+        <v>96</v>
+      </c>
+      <c r="C99" s="10">
+        <v>9600</v>
+      </c>
+      <c r="D99" s="11">
+        <v>48</v>
+      </c>
+      <c r="E99" s="10">
+        <v>48</v>
+      </c>
+      <c r="F99" s="10">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100" s="10">
+        <v>1</v>
+      </c>
+      <c r="B100" s="10">
+        <v>97</v>
+      </c>
+      <c r="C100" s="10">
+        <v>9700</v>
+      </c>
+      <c r="D100" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="E100" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="F100" s="11">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" s="10">
+        <v>1</v>
+      </c>
+      <c r="B101" s="10">
+        <v>98</v>
+      </c>
+      <c r="C101" s="10">
+        <v>9800</v>
+      </c>
+      <c r="D101" s="11">
+        <v>49</v>
+      </c>
+      <c r="E101" s="10">
+        <v>49</v>
+      </c>
+      <c r="F101" s="10">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102" s="10">
+        <v>1</v>
+      </c>
+      <c r="B102" s="10">
+        <v>99</v>
+      </c>
+      <c r="C102" s="10">
+        <v>9900</v>
+      </c>
+      <c r="D102" s="11">
+        <v>49.5</v>
+      </c>
+      <c r="E102" s="11">
+        <v>49.5</v>
+      </c>
+      <c r="F102" s="11">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" s="10">
+        <v>1</v>
+      </c>
+      <c r="B103" s="10">
+        <v>100</v>
+      </c>
+      <c r="C103" s="10">
+        <v>0</v>
+      </c>
+      <c r="D103" s="11">
+        <v>50</v>
+      </c>
+      <c r="E103" s="10">
+        <v>50</v>
+      </c>
+      <c r="F103" s="10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104" s="10">
+        <v>2</v>
+      </c>
+      <c r="B104" s="10">
+        <f>B4</f>
+        <v>1</v>
+      </c>
+      <c r="C104" s="10">
+        <f>C4</f>
+        <v>100</v>
+      </c>
+      <c r="D104" s="11">
+        <v>0.6</v>
+      </c>
+      <c r="E104" s="11">
+        <v>0.6</v>
+      </c>
+      <c r="F104" s="11">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105" s="10">
+        <v>2</v>
+      </c>
+      <c r="B105" s="10">
+        <f t="shared" ref="B105:C168" si="0">B5</f>
+        <v>2</v>
+      </c>
+      <c r="C105" s="10">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="D105" s="11">
+        <v>1.2</v>
+      </c>
+      <c r="E105" s="11">
+        <v>1.2</v>
+      </c>
+      <c r="F105" s="11">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106" s="10">
+        <v>2</v>
+      </c>
+      <c r="B106" s="10">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C106" s="10">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="D106" s="11">
+        <v>1.8</v>
+      </c>
+      <c r="E106" s="11">
+        <v>1.8</v>
+      </c>
+      <c r="F106" s="11">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107" s="10">
+        <v>2</v>
+      </c>
+      <c r="B107" s="10">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C107" s="10">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="D107" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="E107" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="F107" s="11">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A108" s="10">
+        <v>2</v>
+      </c>
+      <c r="B108" s="10">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C108" s="10">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="D108" s="11">
+        <v>3</v>
+      </c>
+      <c r="E108" s="11">
+        <v>3</v>
+      </c>
+      <c r="F108" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109" s="10">
+        <v>2</v>
+      </c>
+      <c r="B109" s="10">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C109" s="10">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
+      <c r="D109" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="E109" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="F109" s="11">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A110" s="10">
+        <v>2</v>
+      </c>
+      <c r="B110" s="10">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C110" s="10">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="D110" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="E110" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="F110" s="11">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A111" s="10">
+        <v>2</v>
+      </c>
+      <c r="B111" s="10">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C111" s="10">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="D111" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="E111" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="F111" s="11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A112" s="10">
+        <v>2</v>
+      </c>
+      <c r="B112" s="10">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C112" s="10">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="D112" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="E112" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="F112" s="11">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A113" s="10">
+        <v>2</v>
+      </c>
+      <c r="B113" s="10">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C113" s="10">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="D113" s="11">
+        <v>6</v>
+      </c>
+      <c r="E113" s="11">
+        <v>6</v>
+      </c>
+      <c r="F113" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A114" s="10">
+        <v>2</v>
+      </c>
+      <c r="B114" s="10">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C114" s="10">
+        <f t="shared" si="0"/>
+        <v>1100</v>
+      </c>
+      <c r="D114" s="11">
+        <v>6.6</v>
+      </c>
+      <c r="E114" s="11">
+        <v>6.6</v>
+      </c>
+      <c r="F114" s="11">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A115" s="10">
+        <v>2</v>
+      </c>
+      <c r="B115" s="10">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C115" s="10">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+      <c r="D115" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="E115" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="F115" s="11">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A116" s="10">
+        <v>2</v>
+      </c>
+      <c r="B116" s="10">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C116" s="10">
+        <f t="shared" si="0"/>
+        <v>1300</v>
+      </c>
+      <c r="D116" s="11">
+        <v>7.8</v>
+      </c>
+      <c r="E116" s="11">
+        <v>7.8</v>
+      </c>
+      <c r="F116" s="11">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A117" s="10">
+        <v>2</v>
+      </c>
+      <c r="B117" s="10">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C117" s="10">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="D117" s="11">
+        <v>8.4</v>
+      </c>
+      <c r="E117" s="11">
+        <v>8.4</v>
+      </c>
+      <c r="F117" s="11">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A118" s="10">
+        <v>2</v>
+      </c>
+      <c r="B118" s="10">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C118" s="10">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="D118" s="11">
+        <v>9</v>
+      </c>
+      <c r="E118" s="11">
+        <v>9</v>
+      </c>
+      <c r="F118" s="11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A119" s="10">
+        <v>2</v>
+      </c>
+      <c r="B119" s="10">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C119" s="10">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+      <c r="D119" s="11">
+        <v>9.6</v>
+      </c>
+      <c r="E119" s="11">
+        <v>9.6</v>
+      </c>
+      <c r="F119" s="11">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A120" s="10">
+        <v>2</v>
+      </c>
+      <c r="B120" s="10">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C120" s="10">
+        <f t="shared" si="0"/>
+        <v>1700</v>
+      </c>
+      <c r="D120" s="11">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E120" s="11">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F120" s="11">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A121" s="10">
+        <v>2</v>
+      </c>
+      <c r="B121" s="10">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C121" s="10">
+        <f t="shared" si="0"/>
+        <v>1800</v>
+      </c>
+      <c r="D121" s="11">
+        <v>10.8</v>
+      </c>
+      <c r="E121" s="11">
+        <v>10.8</v>
+      </c>
+      <c r="F121" s="11">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A122" s="10">
+        <v>2</v>
+      </c>
+      <c r="B122" s="10">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C122" s="10">
+        <f t="shared" si="0"/>
+        <v>1900</v>
+      </c>
+      <c r="D122" s="11">
+        <v>11.4</v>
+      </c>
+      <c r="E122" s="11">
+        <v>11.4</v>
+      </c>
+      <c r="F122" s="11">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A123" s="10">
+        <v>2</v>
+      </c>
+      <c r="B123" s="10">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C123" s="10">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+      <c r="D123" s="11">
+        <v>12</v>
+      </c>
+      <c r="E123" s="11">
+        <v>12</v>
+      </c>
+      <c r="F123" s="11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A124" s="10">
+        <v>2</v>
+      </c>
+      <c r="B124" s="10">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C124" s="10">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="D124" s="11">
+        <v>12.6</v>
+      </c>
+      <c r="E124" s="11">
+        <v>12.6</v>
+      </c>
+      <c r="F124" s="11">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A125" s="10">
+        <v>2</v>
+      </c>
+      <c r="B125" s="10">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C125" s="10">
+        <f t="shared" si="0"/>
+        <v>2200</v>
+      </c>
+      <c r="D125" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="E125" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="F125" s="11">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A126" s="10">
+        <v>2</v>
+      </c>
+      <c r="B126" s="10">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C126" s="10">
+        <f t="shared" si="0"/>
+        <v>2300</v>
+      </c>
+      <c r="D126" s="11">
+        <v>13.8</v>
+      </c>
+      <c r="E126" s="11">
+        <v>13.8</v>
+      </c>
+      <c r="F126" s="11">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A127" s="10">
+        <v>2</v>
+      </c>
+      <c r="B127" s="10">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C127" s="10">
+        <f t="shared" si="0"/>
+        <v>2400</v>
+      </c>
+      <c r="D127" s="11">
+        <v>14.4</v>
+      </c>
+      <c r="E127" s="11">
+        <v>14.4</v>
+      </c>
+      <c r="F127" s="11">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A128" s="10">
+        <v>2</v>
+      </c>
+      <c r="B128" s="10">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C128" s="10">
+        <f t="shared" si="0"/>
+        <v>2500</v>
+      </c>
+      <c r="D128" s="11">
+        <v>15</v>
+      </c>
+      <c r="E128" s="11">
+        <v>15</v>
+      </c>
+      <c r="F128" s="11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A129" s="10">
+        <v>2</v>
+      </c>
+      <c r="B129" s="10">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C129" s="10">
+        <f t="shared" si="0"/>
+        <v>2600</v>
+      </c>
+      <c r="D129" s="11">
+        <v>15.6</v>
+      </c>
+      <c r="E129" s="11">
+        <v>15.6</v>
+      </c>
+      <c r="F129" s="11">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A130" s="10">
+        <v>2</v>
+      </c>
+      <c r="B130" s="10">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C130" s="10">
+        <f t="shared" si="0"/>
+        <v>2700</v>
+      </c>
+      <c r="D130" s="11">
+        <v>16.2</v>
+      </c>
+      <c r="E130" s="11">
+        <v>16.2</v>
+      </c>
+      <c r="F130" s="11">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A131" s="10">
+        <v>2</v>
+      </c>
+      <c r="B131" s="10">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C131" s="10">
+        <f t="shared" si="0"/>
+        <v>2800</v>
+      </c>
+      <c r="D131" s="11">
+        <v>16.8</v>
+      </c>
+      <c r="E131" s="11">
+        <v>16.8</v>
+      </c>
+      <c r="F131" s="11">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A132" s="10">
+        <v>2</v>
+      </c>
+      <c r="B132" s="10">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C132" s="10">
+        <f t="shared" si="0"/>
+        <v>2900</v>
+      </c>
+      <c r="D132" s="11">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="E132" s="11">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="F132" s="11">
+        <v>17.399999999999999</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A133" s="10">
+        <v>2</v>
+      </c>
+      <c r="B133" s="10">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C133" s="10">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="D133" s="11">
+        <v>18</v>
+      </c>
+      <c r="E133" s="11">
+        <v>18</v>
+      </c>
+      <c r="F133" s="11">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A134" s="10">
+        <v>2</v>
+      </c>
+      <c r="B134" s="10">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C134" s="10">
+        <f t="shared" si="0"/>
+        <v>3100</v>
+      </c>
+      <c r="D134" s="11">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="E134" s="11">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="F134" s="11">
+        <v>18.600000000000001</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A135" s="10">
+        <v>2</v>
+      </c>
+      <c r="B135" s="10">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C135" s="10">
+        <f t="shared" si="0"/>
+        <v>3200</v>
+      </c>
+      <c r="D135" s="11">
+        <v>19.2</v>
+      </c>
+      <c r="E135" s="11">
+        <v>19.2</v>
+      </c>
+      <c r="F135" s="11">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A136" s="10">
+        <v>2</v>
+      </c>
+      <c r="B136" s="10">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C136" s="10">
+        <f t="shared" si="0"/>
+        <v>3300</v>
+      </c>
+      <c r="D136" s="11">
+        <v>19.8</v>
+      </c>
+      <c r="E136" s="11">
+        <v>19.8</v>
+      </c>
+      <c r="F136" s="11">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A137" s="10">
+        <v>2</v>
+      </c>
+      <c r="B137" s="10">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C137" s="10">
+        <f t="shared" si="0"/>
+        <v>3400</v>
+      </c>
+      <c r="D137" s="11">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="E137" s="11">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="F137" s="11">
+        <v>20.399999999999999</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A138" s="10">
+        <v>2</v>
+      </c>
+      <c r="B138" s="10">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="C138" s="10">
+        <f t="shared" si="0"/>
+        <v>3500</v>
+      </c>
+      <c r="D138" s="11">
+        <v>21</v>
+      </c>
+      <c r="E138" s="11">
+        <v>21</v>
+      </c>
+      <c r="F138" s="11">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A139" s="10">
+        <v>2</v>
+      </c>
+      <c r="B139" s="10">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C139" s="10">
+        <f t="shared" si="0"/>
+        <v>3600</v>
+      </c>
+      <c r="D139" s="11">
+        <v>21.6</v>
+      </c>
+      <c r="E139" s="11">
+        <v>21.6</v>
+      </c>
+      <c r="F139" s="11">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A140" s="10">
+        <v>2</v>
+      </c>
+      <c r="B140" s="10">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C140" s="10">
+        <f t="shared" si="0"/>
+        <v>3700</v>
+      </c>
+      <c r="D140" s="11">
+        <v>22.2</v>
+      </c>
+      <c r="E140" s="11">
+        <v>22.2</v>
+      </c>
+      <c r="F140" s="11">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A141" s="10">
+        <v>2</v>
+      </c>
+      <c r="B141" s="10">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="C141" s="10">
+        <f t="shared" si="0"/>
+        <v>3800</v>
+      </c>
+      <c r="D141" s="11">
+        <v>22.8</v>
+      </c>
+      <c r="E141" s="11">
+        <v>22.8</v>
+      </c>
+      <c r="F141" s="11">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A142" s="10">
+        <v>2</v>
+      </c>
+      <c r="B142" s="10">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="C142" s="10">
+        <f t="shared" si="0"/>
+        <v>3900</v>
+      </c>
+      <c r="D142" s="11">
+        <v>23.4</v>
+      </c>
+      <c r="E142" s="11">
+        <v>23.4</v>
+      </c>
+      <c r="F142" s="11">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A143" s="10">
+        <v>2</v>
+      </c>
+      <c r="B143" s="10">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="C143" s="10">
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="D143" s="11">
+        <v>24</v>
+      </c>
+      <c r="E143" s="11">
+        <v>24</v>
+      </c>
+      <c r="F143" s="11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A144" s="10">
+        <v>2</v>
+      </c>
+      <c r="B144" s="10">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="C144" s="10">
+        <f t="shared" si="0"/>
+        <v>4100</v>
+      </c>
+      <c r="D144" s="11">
+        <v>24.6</v>
+      </c>
+      <c r="E144" s="11">
+        <v>24.6</v>
+      </c>
+      <c r="F144" s="11">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A145" s="10">
+        <v>2</v>
+      </c>
+      <c r="B145" s="10">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="C145" s="10">
+        <f t="shared" si="0"/>
+        <v>4200</v>
+      </c>
+      <c r="D145" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="E145" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="F145" s="11">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A146" s="10">
+        <v>2</v>
+      </c>
+      <c r="B146" s="10">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="C146" s="10">
+        <f t="shared" si="0"/>
+        <v>4300</v>
+      </c>
+      <c r="D146" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="E146" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="F146" s="11">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A147" s="10">
+        <v>2</v>
+      </c>
+      <c r="B147" s="10">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="C147" s="10">
+        <f t="shared" si="0"/>
+        <v>4400</v>
+      </c>
+      <c r="D147" s="11">
+        <v>26.4</v>
+      </c>
+      <c r="E147" s="11">
+        <v>26.4</v>
+      </c>
+      <c r="F147" s="11">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A148" s="10">
+        <v>2</v>
+      </c>
+      <c r="B148" s="10">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="C148" s="10">
+        <f t="shared" si="0"/>
+        <v>4500</v>
+      </c>
+      <c r="D148" s="11">
+        <v>27</v>
+      </c>
+      <c r="E148" s="11">
+        <v>27</v>
+      </c>
+      <c r="F148" s="11">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A149" s="10">
+        <v>2</v>
+      </c>
+      <c r="B149" s="10">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="C149" s="10">
+        <f t="shared" si="0"/>
+        <v>4600</v>
+      </c>
+      <c r="D149" s="11">
+        <v>27.6</v>
+      </c>
+      <c r="E149" s="11">
+        <v>27.6</v>
+      </c>
+      <c r="F149" s="11">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A150" s="10">
+        <v>2</v>
+      </c>
+      <c r="B150" s="10">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="C150" s="10">
+        <f t="shared" si="0"/>
+        <v>4700</v>
+      </c>
+      <c r="D150" s="11">
+        <v>28.2</v>
+      </c>
+      <c r="E150" s="11">
+        <v>28.2</v>
+      </c>
+      <c r="F150" s="11">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A151" s="10">
+        <v>2</v>
+      </c>
+      <c r="B151" s="10">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="C151" s="10">
+        <f t="shared" si="0"/>
+        <v>4800</v>
+      </c>
+      <c r="D151" s="11">
+        <v>28.8</v>
+      </c>
+      <c r="E151" s="11">
+        <v>28.8</v>
+      </c>
+      <c r="F151" s="11">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A152" s="10">
+        <v>2</v>
+      </c>
+      <c r="B152" s="10">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="C152" s="10">
+        <f t="shared" si="0"/>
+        <v>4900</v>
+      </c>
+      <c r="D152" s="11">
+        <v>29.4</v>
+      </c>
+      <c r="E152" s="11">
+        <v>29.4</v>
+      </c>
+      <c r="F152" s="11">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A153" s="10">
+        <v>2</v>
+      </c>
+      <c r="B153" s="10">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="C153" s="10">
+        <f t="shared" si="0"/>
+        <v>5000</v>
+      </c>
+      <c r="D153" s="11">
+        <v>30</v>
+      </c>
+      <c r="E153" s="11">
+        <v>30</v>
+      </c>
+      <c r="F153" s="11">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A154" s="10">
+        <v>2</v>
+      </c>
+      <c r="B154" s="10">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="C154" s="10">
+        <f t="shared" si="0"/>
+        <v>5100</v>
+      </c>
+      <c r="D154" s="11">
+        <v>30.6</v>
+      </c>
+      <c r="E154" s="11">
+        <v>30.6</v>
+      </c>
+      <c r="F154" s="11">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A155" s="10">
+        <v>2</v>
+      </c>
+      <c r="B155" s="10">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="C155" s="10">
+        <f t="shared" si="0"/>
+        <v>5200</v>
+      </c>
+      <c r="D155" s="11">
+        <v>31.2</v>
+      </c>
+      <c r="E155" s="11">
+        <v>31.2</v>
+      </c>
+      <c r="F155" s="11">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A156" s="10">
+        <v>2</v>
+      </c>
+      <c r="B156" s="10">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="C156" s="10">
+        <f t="shared" si="0"/>
+        <v>5300</v>
+      </c>
+      <c r="D156" s="11">
+        <v>31.8</v>
+      </c>
+      <c r="E156" s="11">
+        <v>31.8</v>
+      </c>
+      <c r="F156" s="11">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A157" s="10">
+        <v>2</v>
+      </c>
+      <c r="B157" s="10">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="C157" s="10">
+        <f t="shared" si="0"/>
+        <v>5400</v>
+      </c>
+      <c r="D157" s="11">
+        <v>32.4</v>
+      </c>
+      <c r="E157" s="11">
+        <v>32.4</v>
+      </c>
+      <c r="F157" s="11">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A158" s="10">
+        <v>2</v>
+      </c>
+      <c r="B158" s="10">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="C158" s="10">
+        <f t="shared" si="0"/>
+        <v>5500</v>
+      </c>
+      <c r="D158" s="11">
+        <v>33</v>
+      </c>
+      <c r="E158" s="11">
+        <v>33</v>
+      </c>
+      <c r="F158" s="11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A159" s="10">
+        <v>2</v>
+      </c>
+      <c r="B159" s="10">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="C159" s="10">
+        <f t="shared" si="0"/>
+        <v>5600</v>
+      </c>
+      <c r="D159" s="11">
+        <v>33.6</v>
+      </c>
+      <c r="E159" s="11">
+        <v>33.6</v>
+      </c>
+      <c r="F159" s="11">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A160" s="10">
+        <v>2</v>
+      </c>
+      <c r="B160" s="10">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="C160" s="10">
+        <f t="shared" si="0"/>
+        <v>5700</v>
+      </c>
+      <c r="D160" s="11">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="E160" s="11">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="F160" s="11">
+        <v>34.200000000000003</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A161" s="10">
+        <v>2</v>
+      </c>
+      <c r="B161" s="10">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="C161" s="10">
+        <f t="shared" si="0"/>
+        <v>5800</v>
+      </c>
+      <c r="D161" s="11">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="E161" s="11">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="F161" s="11">
+        <v>34.799999999999997</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" s="10">
+        <v>2</v>
+      </c>
+      <c r="B162" s="10">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="C162" s="10">
+        <f t="shared" si="0"/>
+        <v>5900</v>
+      </c>
+      <c r="D162" s="11">
+        <v>35.4</v>
+      </c>
+      <c r="E162" s="11">
+        <v>35.4</v>
+      </c>
+      <c r="F162" s="11">
+        <v>35.4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" s="10">
+        <v>2</v>
+      </c>
+      <c r="B163" s="10">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="C163" s="10">
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+      <c r="D163" s="11">
+        <v>36</v>
+      </c>
+      <c r="E163" s="11">
+        <v>36</v>
+      </c>
+      <c r="F163" s="11">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A164" s="10">
+        <v>2</v>
+      </c>
+      <c r="B164" s="10">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="C164" s="10">
+        <f t="shared" si="0"/>
+        <v>6100</v>
+      </c>
+      <c r="D164" s="11">
+        <v>36.6</v>
+      </c>
+      <c r="E164" s="11">
+        <v>36.6</v>
+      </c>
+      <c r="F164" s="11">
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A165" s="10">
+        <v>2</v>
+      </c>
+      <c r="B165" s="10">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="C165" s="10">
+        <f t="shared" si="0"/>
+        <v>6200</v>
+      </c>
+      <c r="D165" s="11">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="E165" s="11">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="F165" s="11">
+        <v>37.200000000000003</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A166" s="10">
+        <v>2</v>
+      </c>
+      <c r="B166" s="10">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="C166" s="10">
+        <f t="shared" si="0"/>
+        <v>6300</v>
+      </c>
+      <c r="D166" s="11">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="E166" s="11">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="F166" s="11">
+        <v>37.799999999999997</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A167" s="10">
+        <v>2</v>
+      </c>
+      <c r="B167" s="10">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="C167" s="10">
+        <f t="shared" si="0"/>
+        <v>6400</v>
+      </c>
+      <c r="D167" s="11">
+        <v>38.4</v>
+      </c>
+      <c r="E167" s="11">
+        <v>38.4</v>
+      </c>
+      <c r="F167" s="11">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A168" s="10">
+        <v>2</v>
+      </c>
+      <c r="B168" s="10">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="C168" s="10">
+        <f t="shared" si="0"/>
+        <v>6500</v>
+      </c>
+      <c r="D168" s="11">
+        <v>39</v>
+      </c>
+      <c r="E168" s="11">
+        <v>39</v>
+      </c>
+      <c r="F168" s="11">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A169" s="10">
+        <v>2</v>
+      </c>
+      <c r="B169" s="10">
+        <f t="shared" ref="B169:C232" si="1">B69</f>
+        <v>66</v>
+      </c>
+      <c r="C169" s="10">
+        <f t="shared" si="1"/>
+        <v>6600</v>
+      </c>
+      <c r="D169" s="11">
+        <v>39.6</v>
+      </c>
+      <c r="E169" s="11">
+        <v>39.6</v>
+      </c>
+      <c r="F169" s="11">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A170" s="10">
+        <v>2</v>
+      </c>
+      <c r="B170" s="10">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="C170" s="10">
+        <f t="shared" si="1"/>
+        <v>6700</v>
+      </c>
+      <c r="D170" s="11">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="E170" s="11">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="F170" s="11">
+        <v>40.200000000000003</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A171" s="10">
+        <v>2</v>
+      </c>
+      <c r="B171" s="10">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="C171" s="10">
+        <f t="shared" si="1"/>
+        <v>6800</v>
+      </c>
+      <c r="D171" s="11">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="E171" s="11">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="F171" s="11">
+        <v>40.799999999999997</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A172" s="10">
+        <v>2</v>
+      </c>
+      <c r="B172" s="10">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="C172" s="10">
+        <f t="shared" si="1"/>
+        <v>6900</v>
+      </c>
+      <c r="D172" s="11">
+        <v>41.4</v>
+      </c>
+      <c r="E172" s="11">
+        <v>41.4</v>
+      </c>
+      <c r="F172" s="11">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A173" s="10">
+        <v>2</v>
+      </c>
+      <c r="B173" s="10">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="C173" s="10">
+        <f t="shared" si="1"/>
+        <v>7000</v>
+      </c>
+      <c r="D173" s="11">
+        <v>42</v>
+      </c>
+      <c r="E173" s="11">
+        <v>42</v>
+      </c>
+      <c r="F173" s="11">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A174" s="10">
+        <v>2</v>
+      </c>
+      <c r="B174" s="10">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="C174" s="10">
+        <f t="shared" si="1"/>
+        <v>7100</v>
+      </c>
+      <c r="D174" s="11">
+        <v>42.6</v>
+      </c>
+      <c r="E174" s="11">
+        <v>42.6</v>
+      </c>
+      <c r="F174" s="11">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A175" s="10">
+        <v>2</v>
+      </c>
+      <c r="B175" s="10">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="C175" s="10">
+        <f t="shared" si="1"/>
+        <v>7200</v>
+      </c>
+      <c r="D175" s="11">
+        <v>43.2</v>
+      </c>
+      <c r="E175" s="11">
+        <v>43.2</v>
+      </c>
+      <c r="F175" s="11">
+        <v>43.2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A176" s="10">
+        <v>2</v>
+      </c>
+      <c r="B176" s="10">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="C176" s="10">
+        <f t="shared" si="1"/>
+        <v>7300</v>
+      </c>
+      <c r="D176" s="11">
+        <v>43.8</v>
+      </c>
+      <c r="E176" s="11">
+        <v>43.8</v>
+      </c>
+      <c r="F176" s="11">
+        <v>43.8</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A177" s="10">
+        <v>2</v>
+      </c>
+      <c r="B177" s="10">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="C177" s="10">
+        <f t="shared" si="1"/>
+        <v>7400</v>
+      </c>
+      <c r="D177" s="11">
+        <v>44.4</v>
+      </c>
+      <c r="E177" s="11">
+        <v>44.4</v>
+      </c>
+      <c r="F177" s="11">
+        <v>44.4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A178" s="10">
+        <v>2</v>
+      </c>
+      <c r="B178" s="10">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="C178" s="10">
+        <f t="shared" si="1"/>
+        <v>7500</v>
+      </c>
+      <c r="D178" s="11">
+        <v>45</v>
+      </c>
+      <c r="E178" s="11">
+        <v>45</v>
+      </c>
+      <c r="F178" s="11">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A179" s="10">
+        <v>2</v>
+      </c>
+      <c r="B179" s="10">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="C179" s="10">
+        <f t="shared" si="1"/>
+        <v>7600</v>
+      </c>
+      <c r="D179" s="11">
+        <v>45.6</v>
+      </c>
+      <c r="E179" s="11">
+        <v>45.6</v>
+      </c>
+      <c r="F179" s="11">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A180" s="10">
+        <v>2</v>
+      </c>
+      <c r="B180" s="10">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="C180" s="10">
+        <f t="shared" si="1"/>
+        <v>7700</v>
+      </c>
+      <c r="D180" s="11">
+        <v>46.2</v>
+      </c>
+      <c r="E180" s="11">
+        <v>46.2</v>
+      </c>
+      <c r="F180" s="11">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A181" s="10">
+        <v>2</v>
+      </c>
+      <c r="B181" s="10">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="C181" s="10">
+        <f t="shared" si="1"/>
+        <v>7800</v>
+      </c>
+      <c r="D181" s="11">
+        <v>46.8</v>
+      </c>
+      <c r="E181" s="11">
+        <v>46.8</v>
+      </c>
+      <c r="F181" s="11">
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A182" s="10">
+        <v>2</v>
+      </c>
+      <c r="B182" s="10">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="C182" s="10">
+        <f t="shared" si="1"/>
+        <v>7900</v>
+      </c>
+      <c r="D182" s="11">
+        <v>47.4</v>
+      </c>
+      <c r="E182" s="11">
+        <v>47.4</v>
+      </c>
+      <c r="F182" s="11">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A183" s="10">
+        <v>2</v>
+      </c>
+      <c r="B183" s="10">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="C183" s="10">
+        <f t="shared" si="1"/>
+        <v>8000</v>
+      </c>
+      <c r="D183" s="11">
+        <v>48</v>
+      </c>
+      <c r="E183" s="11">
+        <v>48</v>
+      </c>
+      <c r="F183" s="11">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A184" s="10">
+        <v>2</v>
+      </c>
+      <c r="B184" s="10">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="C184" s="10">
+        <f t="shared" si="1"/>
+        <v>8100</v>
+      </c>
+      <c r="D184" s="11">
+        <v>48.6</v>
+      </c>
+      <c r="E184" s="11">
+        <v>48.6</v>
+      </c>
+      <c r="F184" s="11">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A185" s="10">
+        <v>2</v>
+      </c>
+      <c r="B185" s="10">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+      <c r="C185" s="10">
+        <f t="shared" si="1"/>
+        <v>8200</v>
+      </c>
+      <c r="D185" s="11">
+        <v>49.2</v>
+      </c>
+      <c r="E185" s="11">
+        <v>49.2</v>
+      </c>
+      <c r="F185" s="11">
+        <v>49.2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A186" s="10">
+        <v>2</v>
+      </c>
+      <c r="B186" s="10">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="C186" s="10">
+        <f t="shared" si="1"/>
+        <v>8300</v>
+      </c>
+      <c r="D186" s="11">
+        <v>49.8</v>
+      </c>
+      <c r="E186" s="11">
+        <v>49.8</v>
+      </c>
+      <c r="F186" s="11">
+        <v>49.8</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A187" s="10">
+        <v>2</v>
+      </c>
+      <c r="B187" s="10">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="C187" s="10">
+        <f t="shared" si="1"/>
+        <v>8400</v>
+      </c>
+      <c r="D187" s="11">
+        <v>50.4</v>
+      </c>
+      <c r="E187" s="11">
+        <v>50.4</v>
+      </c>
+      <c r="F187" s="11">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A188" s="10">
+        <v>2</v>
+      </c>
+      <c r="B188" s="10">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="C188" s="10">
+        <f t="shared" si="1"/>
+        <v>8500</v>
+      </c>
+      <c r="D188" s="11">
+        <v>51</v>
+      </c>
+      <c r="E188" s="11">
+        <v>51</v>
+      </c>
+      <c r="F188" s="11">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A189" s="10">
+        <v>2</v>
+      </c>
+      <c r="B189" s="10">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="C189" s="10">
+        <f t="shared" si="1"/>
+        <v>8600</v>
+      </c>
+      <c r="D189" s="11">
+        <v>51.6</v>
+      </c>
+      <c r="E189" s="11">
+        <v>51.6</v>
+      </c>
+      <c r="F189" s="11">
+        <v>51.6</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A190" s="10">
+        <v>2</v>
+      </c>
+      <c r="B190" s="10">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="C190" s="10">
+        <f t="shared" si="1"/>
+        <v>8700</v>
+      </c>
+      <c r="D190" s="11">
+        <v>52.2</v>
+      </c>
+      <c r="E190" s="11">
+        <v>52.2</v>
+      </c>
+      <c r="F190" s="11">
+        <v>52.2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A191" s="10">
+        <v>2</v>
+      </c>
+      <c r="B191" s="10">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="C191" s="10">
+        <f t="shared" si="1"/>
+        <v>8800</v>
+      </c>
+      <c r="D191" s="11">
+        <v>52.8</v>
+      </c>
+      <c r="E191" s="11">
+        <v>52.8</v>
+      </c>
+      <c r="F191" s="11">
+        <v>52.8</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A192" s="10">
+        <v>2</v>
+      </c>
+      <c r="B192" s="10">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="C192" s="10">
+        <f t="shared" si="1"/>
+        <v>8900</v>
+      </c>
+      <c r="D192" s="11">
+        <v>53.4</v>
+      </c>
+      <c r="E192" s="11">
+        <v>53.4</v>
+      </c>
+      <c r="F192" s="11">
+        <v>53.4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A193" s="10">
+        <v>2</v>
+      </c>
+      <c r="B193" s="10">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="C193" s="10">
+        <f t="shared" si="1"/>
+        <v>9000</v>
+      </c>
+      <c r="D193" s="11">
+        <v>54</v>
+      </c>
+      <c r="E193" s="11">
+        <v>54</v>
+      </c>
+      <c r="F193" s="11">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A194" s="10">
+        <v>2</v>
+      </c>
+      <c r="B194" s="10">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="C194" s="10">
+        <f t="shared" si="1"/>
+        <v>9100</v>
+      </c>
+      <c r="D194" s="11">
+        <v>54.6</v>
+      </c>
+      <c r="E194" s="11">
+        <v>54.6</v>
+      </c>
+      <c r="F194" s="11">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A195" s="10">
+        <v>2</v>
+      </c>
+      <c r="B195" s="10">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="C195" s="10">
+        <f t="shared" si="1"/>
+        <v>9200</v>
+      </c>
+      <c r="D195" s="11">
+        <v>55.2</v>
+      </c>
+      <c r="E195" s="11">
+        <v>55.2</v>
+      </c>
+      <c r="F195" s="11">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A196" s="10">
+        <v>2</v>
+      </c>
+      <c r="B196" s="10">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+      <c r="C196" s="10">
+        <f t="shared" si="1"/>
+        <v>9300</v>
+      </c>
+      <c r="D196" s="11">
+        <v>55.8</v>
+      </c>
+      <c r="E196" s="11">
+        <v>55.8</v>
+      </c>
+      <c r="F196" s="11">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A197" s="10">
+        <v>2</v>
+      </c>
+      <c r="B197" s="10">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="C197" s="10">
+        <f t="shared" si="1"/>
+        <v>9400</v>
+      </c>
+      <c r="D197" s="11">
+        <v>56.4</v>
+      </c>
+      <c r="E197" s="11">
+        <v>56.4</v>
+      </c>
+      <c r="F197" s="11">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A198" s="10">
+        <v>2</v>
+      </c>
+      <c r="B198" s="10">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="C198" s="10">
+        <f t="shared" si="1"/>
+        <v>9500</v>
+      </c>
+      <c r="D198" s="11">
+        <v>57</v>
+      </c>
+      <c r="E198" s="11">
+        <v>57</v>
+      </c>
+      <c r="F198" s="11">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A199" s="10">
+        <v>2</v>
+      </c>
+      <c r="B199" s="10">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="C199" s="10">
+        <f t="shared" si="1"/>
+        <v>9600</v>
+      </c>
+      <c r="D199" s="11">
+        <v>57.6</v>
+      </c>
+      <c r="E199" s="11">
+        <v>57.6</v>
+      </c>
+      <c r="F199" s="11">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A200" s="10">
+        <v>2</v>
+      </c>
+      <c r="B200" s="10">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="C200" s="10">
+        <f t="shared" si="1"/>
+        <v>9700</v>
+      </c>
+      <c r="D200" s="11">
+        <v>58.2</v>
+      </c>
+      <c r="E200" s="11">
+        <v>58.2</v>
+      </c>
+      <c r="F200" s="11">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A201" s="10">
+        <v>2</v>
+      </c>
+      <c r="B201" s="10">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="C201" s="10">
+        <f t="shared" si="1"/>
+        <v>9800</v>
+      </c>
+      <c r="D201" s="11">
+        <v>58.8</v>
+      </c>
+      <c r="E201" s="11">
+        <v>58.8</v>
+      </c>
+      <c r="F201" s="11">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A202" s="10">
+        <v>2</v>
+      </c>
+      <c r="B202" s="10">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+      <c r="C202" s="10">
+        <f t="shared" si="1"/>
+        <v>9900</v>
+      </c>
+      <c r="D202" s="11">
+        <v>59.4</v>
+      </c>
+      <c r="E202" s="11">
+        <v>59.4</v>
+      </c>
+      <c r="F202" s="11">
+        <v>59.4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A203" s="10">
+        <v>2</v>
+      </c>
+      <c r="B203" s="10">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="C203" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D203" s="11">
+        <v>60</v>
+      </c>
+      <c r="E203" s="11">
+        <v>60</v>
+      </c>
+      <c r="F203" s="11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A204" s="10">
+        <v>3</v>
+      </c>
+      <c r="B204" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C204" s="10">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="D204" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="E204" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="F204" s="11">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A205" s="10">
+        <v>3</v>
+      </c>
+      <c r="B205" s="10">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="C205" s="10">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="D205" s="11">
+        <v>1.6</v>
+      </c>
+      <c r="E205" s="11">
+        <v>1.6</v>
+      </c>
+      <c r="F205" s="11">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A206" s="10">
+        <v>3</v>
+      </c>
+      <c r="B206" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="C206" s="10">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="D206" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="E206" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="F206" s="11">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A207" s="10">
+        <v>3</v>
+      </c>
+      <c r="B207" s="10">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="C207" s="10">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+      <c r="D207" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="E207" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F207" s="11">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A208" s="10">
+        <v>3</v>
+      </c>
+      <c r="B208" s="10">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="C208" s="10">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="D208" s="11">
+        <v>4</v>
+      </c>
+      <c r="E208" s="11">
+        <v>4</v>
+      </c>
+      <c r="F208" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A209" s="10">
+        <v>3</v>
+      </c>
+      <c r="B209" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="C209" s="10">
+        <f t="shared" si="1"/>
+        <v>600</v>
+      </c>
+      <c r="D209" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="E209" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="F209" s="11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A210" s="10">
+        <v>3</v>
+      </c>
+      <c r="B210" s="10">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="C210" s="10">
+        <f t="shared" si="1"/>
+        <v>700</v>
+      </c>
+      <c r="D210" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="E210" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="F210" s="11">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A211" s="10">
+        <v>3</v>
+      </c>
+      <c r="B211" s="10">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="C211" s="10">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+      <c r="D211" s="11">
+        <v>6.4</v>
+      </c>
+      <c r="E211" s="11">
+        <v>6.4</v>
+      </c>
+      <c r="F211" s="11">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A212" s="10">
+        <v>3</v>
+      </c>
+      <c r="B212" s="10">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="C212" s="10">
+        <f t="shared" si="1"/>
+        <v>900</v>
+      </c>
+      <c r="D212" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="E212" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="F212" s="11">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A213" s="10">
+        <v>3</v>
+      </c>
+      <c r="B213" s="10">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="C213" s="10">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="D213" s="11">
+        <v>8</v>
+      </c>
+      <c r="E213" s="11">
+        <v>8</v>
+      </c>
+      <c r="F213" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A214" s="10">
+        <v>3</v>
+      </c>
+      <c r="B214" s="10">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="C214" s="10">
+        <f t="shared" si="1"/>
+        <v>1100</v>
+      </c>
+      <c r="D214" s="11">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E214" s="11">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="F214" s="11">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A215" s="10">
+        <v>3</v>
+      </c>
+      <c r="B215" s="10">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="C215" s="10">
+        <f t="shared" si="1"/>
+        <v>1200</v>
+      </c>
+      <c r="D215" s="11">
+        <v>9.6</v>
+      </c>
+      <c r="E215" s="11">
+        <v>9.6</v>
+      </c>
+      <c r="F215" s="11">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A216" s="10">
+        <v>3</v>
+      </c>
+      <c r="B216" s="10">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="C216" s="10">
+        <f t="shared" si="1"/>
+        <v>1300</v>
+      </c>
+      <c r="D216" s="11">
+        <v>10.4</v>
+      </c>
+      <c r="E216" s="11">
+        <v>10.4</v>
+      </c>
+      <c r="F216" s="11">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A217" s="10">
+        <v>3</v>
+      </c>
+      <c r="B217" s="10">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="C217" s="10">
+        <f t="shared" si="1"/>
+        <v>1400</v>
+      </c>
+      <c r="D217" s="11">
+        <v>11.2</v>
+      </c>
+      <c r="E217" s="11">
+        <v>11.2</v>
+      </c>
+      <c r="F217" s="11">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A218" s="10">
+        <v>3</v>
+      </c>
+      <c r="B218" s="10">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="C218" s="10">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="D218" s="11">
+        <v>12</v>
+      </c>
+      <c r="E218" s="11">
+        <v>12</v>
+      </c>
+      <c r="F218" s="11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A219" s="10">
+        <v>3</v>
+      </c>
+      <c r="B219" s="10">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="C219" s="10">
+        <f t="shared" si="1"/>
+        <v>1600</v>
+      </c>
+      <c r="D219" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="E219" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="F219" s="11">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A220" s="10">
+        <v>3</v>
+      </c>
+      <c r="B220" s="10">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="C220" s="10">
+        <f t="shared" si="1"/>
+        <v>1700</v>
+      </c>
+      <c r="D220" s="11">
+        <v>13.6</v>
+      </c>
+      <c r="E220" s="11">
+        <v>13.6</v>
+      </c>
+      <c r="F220" s="11">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A221" s="10">
+        <v>3</v>
+      </c>
+      <c r="B221" s="10">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="C221" s="10">
+        <f t="shared" si="1"/>
+        <v>1800</v>
+      </c>
+      <c r="D221" s="11">
+        <v>14.4</v>
+      </c>
+      <c r="E221" s="11">
+        <v>14.4</v>
+      </c>
+      <c r="F221" s="11">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A222" s="10">
+        <v>3</v>
+      </c>
+      <c r="B222" s="10">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="C222" s="10">
+        <f t="shared" si="1"/>
+        <v>1900</v>
+      </c>
+      <c r="D222" s="11">
+        <v>15.2</v>
+      </c>
+      <c r="E222" s="11">
+        <v>15.2</v>
+      </c>
+      <c r="F222" s="11">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A223" s="10">
+        <v>3</v>
+      </c>
+      <c r="B223" s="10">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="C223" s="10">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="D223" s="11">
+        <v>16</v>
+      </c>
+      <c r="E223" s="11">
+        <v>16</v>
+      </c>
+      <c r="F223" s="11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A224" s="10">
+        <v>3</v>
+      </c>
+      <c r="B224" s="10">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="C224" s="10">
+        <f t="shared" si="1"/>
+        <v>2100</v>
+      </c>
+      <c r="D224" s="11">
+        <v>16.8</v>
+      </c>
+      <c r="E224" s="11">
+        <v>16.8</v>
+      </c>
+      <c r="F224" s="11">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A225" s="10">
+        <v>3</v>
+      </c>
+      <c r="B225" s="10">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="C225" s="10">
+        <f t="shared" si="1"/>
+        <v>2200</v>
+      </c>
+      <c r="D225" s="11">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="E225" s="11">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="F225" s="11">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A226" s="10">
+        <v>3</v>
+      </c>
+      <c r="B226" s="10">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="C226" s="10">
+        <f t="shared" si="1"/>
+        <v>2300</v>
+      </c>
+      <c r="D226" s="11">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="E226" s="11">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="F226" s="11">
+        <v>18.399999999999999</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A227" s="10">
+        <v>3</v>
+      </c>
+      <c r="B227" s="10">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="C227" s="10">
+        <f t="shared" si="1"/>
+        <v>2400</v>
+      </c>
+      <c r="D227" s="11">
+        <v>19.2</v>
+      </c>
+      <c r="E227" s="11">
+        <v>19.2</v>
+      </c>
+      <c r="F227" s="11">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A228" s="10">
+        <v>3</v>
+      </c>
+      <c r="B228" s="10">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="C228" s="10">
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="D228" s="11">
+        <v>20</v>
+      </c>
+      <c r="E228" s="11">
+        <v>20</v>
+      </c>
+      <c r="F228" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A229" s="10">
+        <v>3</v>
+      </c>
+      <c r="B229" s="10">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="C229" s="10">
+        <f t="shared" si="1"/>
+        <v>2600</v>
+      </c>
+      <c r="D229" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="E229" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="F229" s="11">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A230" s="10">
+        <v>3</v>
+      </c>
+      <c r="B230" s="10">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="C230" s="10">
+        <f t="shared" si="1"/>
+        <v>2700</v>
+      </c>
+      <c r="D230" s="11">
+        <v>21.6</v>
+      </c>
+      <c r="E230" s="11">
+        <v>21.6</v>
+      </c>
+      <c r="F230" s="11">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A231" s="10">
+        <v>3</v>
+      </c>
+      <c r="B231" s="10">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="C231" s="10">
+        <f t="shared" si="1"/>
+        <v>2800</v>
+      </c>
+      <c r="D231" s="11">
+        <v>22.4</v>
+      </c>
+      <c r="E231" s="11">
+        <v>22.4</v>
+      </c>
+      <c r="F231" s="11">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A232" s="10">
+        <v>3</v>
+      </c>
+      <c r="B232" s="10">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="C232" s="10">
+        <f t="shared" si="1"/>
+        <v>2900</v>
+      </c>
+      <c r="D232" s="11">
+        <v>23.2</v>
+      </c>
+      <c r="E232" s="11">
+        <v>23.2</v>
+      </c>
+      <c r="F232" s="11">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A233" s="10">
+        <v>3</v>
+      </c>
+      <c r="B233" s="10">
+        <f t="shared" ref="B233:C296" si="2">B133</f>
+        <v>30</v>
+      </c>
+      <c r="C233" s="10">
+        <f t="shared" si="2"/>
+        <v>3000</v>
+      </c>
+      <c r="D233" s="11">
+        <v>24</v>
+      </c>
+      <c r="E233" s="11">
+        <v>24</v>
+      </c>
+      <c r="F233" s="11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A234" s="10">
+        <v>3</v>
+      </c>
+      <c r="B234" s="10">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="C234" s="10">
+        <f t="shared" si="2"/>
+        <v>3100</v>
+      </c>
+      <c r="D234" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="E234" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="F234" s="11">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A235" s="10">
+        <v>3</v>
+      </c>
+      <c r="B235" s="10">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="C235" s="10">
+        <f t="shared" si="2"/>
+        <v>3200</v>
+      </c>
+      <c r="D235" s="11">
+        <v>25.6</v>
+      </c>
+      <c r="E235" s="11">
+        <v>25.6</v>
+      </c>
+      <c r="F235" s="11">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A236" s="10">
+        <v>3</v>
+      </c>
+      <c r="B236" s="10">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="C236" s="10">
+        <f t="shared" si="2"/>
+        <v>3300</v>
+      </c>
+      <c r="D236" s="11">
+        <v>26.4</v>
+      </c>
+      <c r="E236" s="11">
+        <v>26.4</v>
+      </c>
+      <c r="F236" s="11">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A237" s="10">
+        <v>3</v>
+      </c>
+      <c r="B237" s="10">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="C237" s="10">
+        <f t="shared" si="2"/>
+        <v>3400</v>
+      </c>
+      <c r="D237" s="11">
+        <v>27.2</v>
+      </c>
+      <c r="E237" s="11">
+        <v>27.2</v>
+      </c>
+      <c r="F237" s="11">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A238" s="10">
+        <v>3</v>
+      </c>
+      <c r="B238" s="10">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="C238" s="10">
+        <f t="shared" si="2"/>
+        <v>3500</v>
+      </c>
+      <c r="D238" s="11">
+        <v>28</v>
+      </c>
+      <c r="E238" s="11">
+        <v>28</v>
+      </c>
+      <c r="F238" s="11">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A239" s="10">
+        <v>3</v>
+      </c>
+      <c r="B239" s="10">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="C239" s="10">
+        <f t="shared" si="2"/>
+        <v>3600</v>
+      </c>
+      <c r="D239" s="11">
+        <v>28.8</v>
+      </c>
+      <c r="E239" s="11">
+        <v>28.8</v>
+      </c>
+      <c r="F239" s="11">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A240" s="10">
+        <v>3</v>
+      </c>
+      <c r="B240" s="10">
+        <f t="shared" si="2"/>
+        <v>37</v>
+      </c>
+      <c r="C240" s="10">
+        <f t="shared" si="2"/>
+        <v>3700</v>
+      </c>
+      <c r="D240" s="11">
+        <v>29.6</v>
+      </c>
+      <c r="E240" s="11">
+        <v>29.6</v>
+      </c>
+      <c r="F240" s="11">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A241" s="10">
+        <v>3</v>
+      </c>
+      <c r="B241" s="10">
+        <f t="shared" si="2"/>
+        <v>38</v>
+      </c>
+      <c r="C241" s="10">
+        <f t="shared" si="2"/>
+        <v>3800</v>
+      </c>
+      <c r="D241" s="11">
+        <v>30.4</v>
+      </c>
+      <c r="E241" s="11">
+        <v>30.4</v>
+      </c>
+      <c r="F241" s="11">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A242" s="10">
+        <v>3</v>
+      </c>
+      <c r="B242" s="10">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="C242" s="10">
+        <f t="shared" si="2"/>
+        <v>3900</v>
+      </c>
+      <c r="D242" s="11">
+        <v>31.2</v>
+      </c>
+      <c r="E242" s="11">
+        <v>31.2</v>
+      </c>
+      <c r="F242" s="11">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A243" s="10">
+        <v>3</v>
+      </c>
+      <c r="B243" s="10">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="C243" s="10">
+        <f t="shared" si="2"/>
+        <v>4000</v>
+      </c>
+      <c r="D243" s="11">
+        <v>32</v>
+      </c>
+      <c r="E243" s="11">
+        <v>32</v>
+      </c>
+      <c r="F243" s="11">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A244" s="10">
+        <v>3</v>
+      </c>
+      <c r="B244" s="10">
+        <f t="shared" si="2"/>
+        <v>41</v>
+      </c>
+      <c r="C244" s="10">
+        <f t="shared" si="2"/>
+        <v>4100</v>
+      </c>
+      <c r="D244" s="11">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="E244" s="11">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F244" s="11">
+        <v>32.799999999999997</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A245" s="10">
+        <v>3</v>
+      </c>
+      <c r="B245" s="10">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="C245" s="10">
+        <f t="shared" si="2"/>
+        <v>4200</v>
+      </c>
+      <c r="D245" s="11">
+        <v>33.6</v>
+      </c>
+      <c r="E245" s="11">
+        <v>33.6</v>
+      </c>
+      <c r="F245" s="11">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A246" s="10">
+        <v>3</v>
+      </c>
+      <c r="B246" s="10">
+        <f t="shared" si="2"/>
+        <v>43</v>
+      </c>
+      <c r="C246" s="10">
+        <f t="shared" si="2"/>
+        <v>4300</v>
+      </c>
+      <c r="D246" s="11">
+        <v>34.4</v>
+      </c>
+      <c r="E246" s="11">
+        <v>34.4</v>
+      </c>
+      <c r="F246" s="11">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A247" s="10">
+        <v>3</v>
+      </c>
+      <c r="B247" s="10">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="C247" s="10">
+        <f t="shared" si="2"/>
+        <v>4400</v>
+      </c>
+      <c r="D247" s="11">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="E247" s="11">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="F247" s="11">
+        <v>35.200000000000003</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A248" s="10">
+        <v>3</v>
+      </c>
+      <c r="B248" s="10">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="C248" s="10">
+        <f t="shared" si="2"/>
+        <v>4500</v>
+      </c>
+      <c r="D248" s="11">
+        <v>36</v>
+      </c>
+      <c r="E248" s="11">
+        <v>36</v>
+      </c>
+      <c r="F248" s="11">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A249" s="10">
+        <v>3</v>
+      </c>
+      <c r="B249" s="10">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+      <c r="C249" s="10">
+        <f t="shared" si="2"/>
+        <v>4600</v>
+      </c>
+      <c r="D249" s="11">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="E249" s="11">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="F249" s="11">
+        <v>36.799999999999997</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A250" s="10">
+        <v>3</v>
+      </c>
+      <c r="B250" s="10">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+      <c r="C250" s="10">
+        <f t="shared" si="2"/>
+        <v>4700</v>
+      </c>
+      <c r="D250" s="11">
+        <v>37.6</v>
+      </c>
+      <c r="E250" s="11">
+        <v>37.6</v>
+      </c>
+      <c r="F250" s="11">
+        <v>37.6</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A251" s="10">
+        <v>3</v>
+      </c>
+      <c r="B251" s="10">
+        <f t="shared" si="2"/>
+        <v>48</v>
+      </c>
+      <c r="C251" s="10">
+        <f t="shared" si="2"/>
+        <v>4800</v>
+      </c>
+      <c r="D251" s="11">
+        <v>38.4</v>
+      </c>
+      <c r="E251" s="11">
+        <v>38.4</v>
+      </c>
+      <c r="F251" s="11">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A252" s="10">
+        <v>3</v>
+      </c>
+      <c r="B252" s="10">
+        <f t="shared" si="2"/>
+        <v>49</v>
+      </c>
+      <c r="C252" s="10">
+        <f t="shared" si="2"/>
+        <v>4900</v>
+      </c>
+      <c r="D252" s="11">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="E252" s="11">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="F252" s="11">
+        <v>39.200000000000003</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A253" s="10">
+        <v>3</v>
+      </c>
+      <c r="B253" s="10">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="C253" s="10">
+        <f t="shared" si="2"/>
+        <v>5000</v>
+      </c>
+      <c r="D253" s="11">
+        <v>40</v>
+      </c>
+      <c r="E253" s="11">
+        <v>40</v>
+      </c>
+      <c r="F253" s="11">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A254" s="10">
+        <v>3</v>
+      </c>
+      <c r="B254" s="10">
+        <f t="shared" si="2"/>
+        <v>51</v>
+      </c>
+      <c r="C254" s="10">
+        <f t="shared" si="2"/>
+        <v>5100</v>
+      </c>
+      <c r="D254" s="11">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="E254" s="11">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="F254" s="11">
+        <v>40.799999999999997</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A255" s="10">
+        <v>3</v>
+      </c>
+      <c r="B255" s="10">
+        <f t="shared" si="2"/>
+        <v>52</v>
+      </c>
+      <c r="C255" s="10">
+        <f t="shared" si="2"/>
+        <v>5200</v>
+      </c>
+      <c r="D255" s="11">
+        <v>41.6</v>
+      </c>
+      <c r="E255" s="11">
+        <v>41.6</v>
+      </c>
+      <c r="F255" s="11">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A256" s="10">
+        <v>3</v>
+      </c>
+      <c r="B256" s="10">
+        <f t="shared" si="2"/>
+        <v>53</v>
+      </c>
+      <c r="C256" s="10">
+        <f t="shared" si="2"/>
+        <v>5300</v>
+      </c>
+      <c r="D256" s="11">
+        <v>42.4</v>
+      </c>
+      <c r="E256" s="11">
+        <v>42.4</v>
+      </c>
+      <c r="F256" s="11">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A257" s="10">
+        <v>3</v>
+      </c>
+      <c r="B257" s="10">
+        <f t="shared" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="C257" s="10">
+        <f t="shared" si="2"/>
+        <v>5400</v>
+      </c>
+      <c r="D257" s="11">
+        <v>43.2</v>
+      </c>
+      <c r="E257" s="11">
+        <v>43.2</v>
+      </c>
+      <c r="F257" s="11">
+        <v>43.2</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A258" s="10">
+        <v>3</v>
+      </c>
+      <c r="B258" s="10">
+        <f t="shared" si="2"/>
+        <v>55</v>
+      </c>
+      <c r="C258" s="10">
+        <f t="shared" si="2"/>
+        <v>5500</v>
+      </c>
+      <c r="D258" s="11">
+        <v>44</v>
+      </c>
+      <c r="E258" s="11">
+        <v>44</v>
+      </c>
+      <c r="F258" s="11">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A259" s="10">
+        <v>3</v>
+      </c>
+      <c r="B259" s="10">
+        <f t="shared" si="2"/>
+        <v>56</v>
+      </c>
+      <c r="C259" s="10">
+        <f t="shared" si="2"/>
+        <v>5600</v>
+      </c>
+      <c r="D259" s="11">
+        <v>44.8</v>
+      </c>
+      <c r="E259" s="11">
+        <v>44.8</v>
+      </c>
+      <c r="F259" s="11">
+        <v>44.8</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A260" s="10">
+        <v>3</v>
+      </c>
+      <c r="B260" s="10">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="C260" s="10">
+        <f t="shared" si="2"/>
+        <v>5700</v>
+      </c>
+      <c r="D260" s="11">
+        <v>45.6</v>
+      </c>
+      <c r="E260" s="11">
+        <v>45.6</v>
+      </c>
+      <c r="F260" s="11">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A261" s="10">
+        <v>3</v>
+      </c>
+      <c r="B261" s="10">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="C261" s="10">
+        <f t="shared" si="2"/>
+        <v>5800</v>
+      </c>
+      <c r="D261" s="11">
+        <v>46.4</v>
+      </c>
+      <c r="E261" s="11">
+        <v>46.4</v>
+      </c>
+      <c r="F261" s="11">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A262" s="10">
+        <v>3</v>
+      </c>
+      <c r="B262" s="10">
+        <f t="shared" si="2"/>
+        <v>59</v>
+      </c>
+      <c r="C262" s="10">
+        <f t="shared" si="2"/>
+        <v>5900</v>
+      </c>
+      <c r="D262" s="11">
+        <v>47.2</v>
+      </c>
+      <c r="E262" s="11">
+        <v>47.2</v>
+      </c>
+      <c r="F262" s="11">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A263" s="10">
+        <v>3</v>
+      </c>
+      <c r="B263" s="10">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="C263" s="10">
+        <f t="shared" si="2"/>
+        <v>6000</v>
+      </c>
+      <c r="D263" s="11">
+        <v>48</v>
+      </c>
+      <c r="E263" s="11">
+        <v>48</v>
+      </c>
+      <c r="F263" s="11">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A264" s="10">
+        <v>3</v>
+      </c>
+      <c r="B264" s="10">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="C264" s="10">
+        <f t="shared" si="2"/>
+        <v>6100</v>
+      </c>
+      <c r="D264" s="11">
+        <v>48.8</v>
+      </c>
+      <c r="E264" s="11">
+        <v>48.8</v>
+      </c>
+      <c r="F264" s="11">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A265" s="10">
+        <v>3</v>
+      </c>
+      <c r="B265" s="10">
+        <f t="shared" si="2"/>
+        <v>62</v>
+      </c>
+      <c r="C265" s="10">
+        <f t="shared" si="2"/>
+        <v>6200</v>
+      </c>
+      <c r="D265" s="11">
+        <v>49.6</v>
+      </c>
+      <c r="E265" s="11">
+        <v>49.6</v>
+      </c>
+      <c r="F265" s="11">
+        <v>49.6</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A266" s="10">
+        <v>3</v>
+      </c>
+      <c r="B266" s="10">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="C266" s="10">
+        <f t="shared" si="2"/>
+        <v>6300</v>
+      </c>
+      <c r="D266" s="11">
+        <v>50.4</v>
+      </c>
+      <c r="E266" s="11">
+        <v>50.4</v>
+      </c>
+      <c r="F266" s="11">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A267" s="10">
+        <v>3</v>
+      </c>
+      <c r="B267" s="10">
+        <f t="shared" si="2"/>
+        <v>64</v>
+      </c>
+      <c r="C267" s="10">
+        <f t="shared" si="2"/>
+        <v>6400</v>
+      </c>
+      <c r="D267" s="11">
+        <v>51.2</v>
+      </c>
+      <c r="E267" s="11">
+        <v>51.2</v>
+      </c>
+      <c r="F267" s="11">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A268" s="10">
+        <v>3</v>
+      </c>
+      <c r="B268" s="10">
+        <f t="shared" si="2"/>
+        <v>65</v>
+      </c>
+      <c r="C268" s="10">
+        <f t="shared" si="2"/>
+        <v>6500</v>
+      </c>
+      <c r="D268" s="11">
+        <v>52</v>
+      </c>
+      <c r="E268" s="11">
+        <v>52</v>
+      </c>
+      <c r="F268" s="11">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A269" s="10">
+        <v>3</v>
+      </c>
+      <c r="B269" s="10">
+        <f t="shared" si="2"/>
+        <v>66</v>
+      </c>
+      <c r="C269" s="10">
+        <f t="shared" si="2"/>
+        <v>6600</v>
+      </c>
+      <c r="D269" s="11">
+        <v>52.8</v>
+      </c>
+      <c r="E269" s="11">
+        <v>52.8</v>
+      </c>
+      <c r="F269" s="11">
+        <v>52.8</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A270" s="10">
+        <v>3</v>
+      </c>
+      <c r="B270" s="10">
+        <f t="shared" si="2"/>
+        <v>67</v>
+      </c>
+      <c r="C270" s="10">
+        <f t="shared" si="2"/>
+        <v>6700</v>
+      </c>
+      <c r="D270" s="11">
+        <v>53.6</v>
+      </c>
+      <c r="E270" s="11">
+        <v>53.6</v>
+      </c>
+      <c r="F270" s="11">
+        <v>53.6</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A271" s="10">
+        <v>3</v>
+      </c>
+      <c r="B271" s="10">
+        <f t="shared" si="2"/>
+        <v>68</v>
+      </c>
+      <c r="C271" s="10">
+        <f t="shared" si="2"/>
+        <v>6800</v>
+      </c>
+      <c r="D271" s="11">
+        <v>54.4</v>
+      </c>
+      <c r="E271" s="11">
+        <v>54.4</v>
+      </c>
+      <c r="F271" s="11">
+        <v>54.4</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A272" s="10">
+        <v>3</v>
+      </c>
+      <c r="B272" s="10">
+        <f t="shared" si="2"/>
+        <v>69</v>
+      </c>
+      <c r="C272" s="10">
+        <f t="shared" si="2"/>
+        <v>6900</v>
+      </c>
+      <c r="D272" s="11">
+        <v>55.2</v>
+      </c>
+      <c r="E272" s="11">
+        <v>55.2</v>
+      </c>
+      <c r="F272" s="11">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A273" s="10">
+        <v>3</v>
+      </c>
+      <c r="B273" s="10">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="C273" s="10">
+        <f t="shared" si="2"/>
+        <v>7000</v>
+      </c>
+      <c r="D273" s="11">
+        <v>56</v>
+      </c>
+      <c r="E273" s="11">
+        <v>56</v>
+      </c>
+      <c r="F273" s="11">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A274" s="10">
+        <v>3</v>
+      </c>
+      <c r="B274" s="10">
+        <f t="shared" si="2"/>
+        <v>71</v>
+      </c>
+      <c r="C274" s="10">
+        <f t="shared" si="2"/>
+        <v>7100</v>
+      </c>
+      <c r="D274" s="11">
+        <v>56.8</v>
+      </c>
+      <c r="E274" s="11">
+        <v>56.8</v>
+      </c>
+      <c r="F274" s="11">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A275" s="10">
+        <v>3</v>
+      </c>
+      <c r="B275" s="10">
+        <f t="shared" si="2"/>
+        <v>72</v>
+      </c>
+      <c r="C275" s="10">
+        <f t="shared" si="2"/>
+        <v>7200</v>
+      </c>
+      <c r="D275" s="11">
+        <v>57.6</v>
+      </c>
+      <c r="E275" s="11">
+        <v>57.6</v>
+      </c>
+      <c r="F275" s="11">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A276" s="10">
+        <v>3</v>
+      </c>
+      <c r="B276" s="10">
+        <f t="shared" si="2"/>
+        <v>73</v>
+      </c>
+      <c r="C276" s="10">
+        <f t="shared" si="2"/>
+        <v>7300</v>
+      </c>
+      <c r="D276" s="11">
+        <v>58.4</v>
+      </c>
+      <c r="E276" s="11">
+        <v>58.4</v>
+      </c>
+      <c r="F276" s="11">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A277" s="10">
+        <v>3</v>
+      </c>
+      <c r="B277" s="10">
+        <f t="shared" si="2"/>
+        <v>74</v>
+      </c>
+      <c r="C277" s="10">
+        <f t="shared" si="2"/>
+        <v>7400</v>
+      </c>
+      <c r="D277" s="11">
+        <v>59.2</v>
+      </c>
+      <c r="E277" s="11">
+        <v>59.2</v>
+      </c>
+      <c r="F277" s="11">
+        <v>59.2</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A278" s="10">
+        <v>3</v>
+      </c>
+      <c r="B278" s="10">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+      <c r="C278" s="10">
+        <f t="shared" si="2"/>
+        <v>7500</v>
+      </c>
+      <c r="D278" s="11">
+        <v>60</v>
+      </c>
+      <c r="E278" s="11">
+        <v>60</v>
+      </c>
+      <c r="F278" s="11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A279" s="10">
+        <v>3</v>
+      </c>
+      <c r="B279" s="10">
+        <f t="shared" si="2"/>
+        <v>76</v>
+      </c>
+      <c r="C279" s="10">
+        <f t="shared" si="2"/>
+        <v>7600</v>
+      </c>
+      <c r="D279" s="11">
+        <v>60.8</v>
+      </c>
+      <c r="E279" s="11">
+        <v>60.8</v>
+      </c>
+      <c r="F279" s="11">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A280" s="10">
+        <v>3</v>
+      </c>
+      <c r="B280" s="10">
+        <f t="shared" si="2"/>
+        <v>77</v>
+      </c>
+      <c r="C280" s="10">
+        <f t="shared" si="2"/>
+        <v>7700</v>
+      </c>
+      <c r="D280" s="11">
+        <v>61.6</v>
+      </c>
+      <c r="E280" s="11">
+        <v>61.6</v>
+      </c>
+      <c r="F280" s="11">
+        <v>61.6</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A281" s="10">
+        <v>3</v>
+      </c>
+      <c r="B281" s="10">
+        <f t="shared" si="2"/>
+        <v>78</v>
+      </c>
+      <c r="C281" s="10">
+        <f t="shared" si="2"/>
+        <v>7800</v>
+      </c>
+      <c r="D281" s="11">
+        <v>62.4</v>
+      </c>
+      <c r="E281" s="11">
+        <v>62.4</v>
+      </c>
+      <c r="F281" s="11">
+        <v>62.4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A282" s="10">
+        <v>3</v>
+      </c>
+      <c r="B282" s="10">
+        <f t="shared" si="2"/>
+        <v>79</v>
+      </c>
+      <c r="C282" s="10">
+        <f t="shared" si="2"/>
+        <v>7900</v>
+      </c>
+      <c r="D282" s="11">
+        <v>63.2</v>
+      </c>
+      <c r="E282" s="11">
+        <v>63.2</v>
+      </c>
+      <c r="F282" s="11">
+        <v>63.2</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A283" s="10">
+        <v>3</v>
+      </c>
+      <c r="B283" s="10">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="C283" s="10">
+        <f t="shared" si="2"/>
+        <v>8000</v>
+      </c>
+      <c r="D283" s="11">
+        <v>64</v>
+      </c>
+      <c r="E283" s="11">
+        <v>64</v>
+      </c>
+      <c r="F283" s="11">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A284" s="10">
+        <v>3</v>
+      </c>
+      <c r="B284" s="10">
+        <f t="shared" si="2"/>
+        <v>81</v>
+      </c>
+      <c r="C284" s="10">
+        <f t="shared" si="2"/>
+        <v>8100</v>
+      </c>
+      <c r="D284" s="11">
+        <v>64.8</v>
+      </c>
+      <c r="E284" s="11">
+        <v>64.8</v>
+      </c>
+      <c r="F284" s="11">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A285" s="10">
+        <v>3</v>
+      </c>
+      <c r="B285" s="10">
+        <f t="shared" si="2"/>
+        <v>82</v>
+      </c>
+      <c r="C285" s="10">
+        <f t="shared" si="2"/>
+        <v>8200</v>
+      </c>
+      <c r="D285" s="11">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="E285" s="11">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="F285" s="11">
+        <v>65.599999999999994</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A286" s="10">
+        <v>3</v>
+      </c>
+      <c r="B286" s="10">
+        <f t="shared" si="2"/>
+        <v>83</v>
+      </c>
+      <c r="C286" s="10">
+        <f t="shared" si="2"/>
+        <v>8300</v>
+      </c>
+      <c r="D286" s="11">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="E286" s="11">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="F286" s="11">
+        <v>66.400000000000006</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A287" s="10">
+        <v>3</v>
+      </c>
+      <c r="B287" s="10">
+        <f t="shared" si="2"/>
+        <v>84</v>
+      </c>
+      <c r="C287" s="10">
+        <f t="shared" si="2"/>
+        <v>8400</v>
+      </c>
+      <c r="D287" s="11">
+        <v>67.2</v>
+      </c>
+      <c r="E287" s="11">
+        <v>67.2</v>
+      </c>
+      <c r="F287" s="11">
+        <v>67.2</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A288" s="10">
+        <v>3</v>
+      </c>
+      <c r="B288" s="10">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="C288" s="10">
+        <f t="shared" si="2"/>
+        <v>8500</v>
+      </c>
+      <c r="D288" s="11">
+        <v>68</v>
+      </c>
+      <c r="E288" s="11">
+        <v>68</v>
+      </c>
+      <c r="F288" s="11">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A289" s="10">
+        <v>3</v>
+      </c>
+      <c r="B289" s="10">
+        <f t="shared" si="2"/>
+        <v>86</v>
+      </c>
+      <c r="C289" s="10">
+        <f t="shared" si="2"/>
+        <v>8600</v>
+      </c>
+      <c r="D289" s="11">
+        <v>68.8</v>
+      </c>
+      <c r="E289" s="11">
+        <v>68.8</v>
+      </c>
+      <c r="F289" s="11">
+        <v>68.8</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A290" s="10">
+        <v>3</v>
+      </c>
+      <c r="B290" s="10">
+        <f t="shared" si="2"/>
+        <v>87</v>
+      </c>
+      <c r="C290" s="10">
+        <f t="shared" si="2"/>
+        <v>8700</v>
+      </c>
+      <c r="D290" s="11">
+        <v>69.599999999999994</v>
+      </c>
+      <c r="E290" s="11">
+        <v>69.599999999999994</v>
+      </c>
+      <c r="F290" s="11">
+        <v>69.599999999999994</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A291" s="10">
+        <v>3</v>
+      </c>
+      <c r="B291" s="10">
+        <f t="shared" si="2"/>
+        <v>88</v>
+      </c>
+      <c r="C291" s="10">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
+      <c r="D291" s="11">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="E291" s="11">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="F291" s="11">
+        <v>70.400000000000006</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A292" s="10">
+        <v>3</v>
+      </c>
+      <c r="B292" s="10">
+        <f t="shared" si="2"/>
+        <v>89</v>
+      </c>
+      <c r="C292" s="10">
+        <f t="shared" si="2"/>
+        <v>8900</v>
+      </c>
+      <c r="D292" s="11">
+        <v>71.2</v>
+      </c>
+      <c r="E292" s="11">
+        <v>71.2</v>
+      </c>
+      <c r="F292" s="11">
+        <v>71.2</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A293" s="10">
+        <v>3</v>
+      </c>
+      <c r="B293" s="10">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="C293" s="10">
+        <f t="shared" si="2"/>
+        <v>9000</v>
+      </c>
+      <c r="D293" s="11">
+        <v>72</v>
+      </c>
+      <c r="E293" s="11">
+        <v>72</v>
+      </c>
+      <c r="F293" s="11">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A294" s="10">
+        <v>3</v>
+      </c>
+      <c r="B294" s="10">
+        <f t="shared" si="2"/>
+        <v>91</v>
+      </c>
+      <c r="C294" s="10">
+        <f t="shared" si="2"/>
+        <v>9100</v>
+      </c>
+      <c r="D294" s="11">
+        <v>72.8</v>
+      </c>
+      <c r="E294" s="11">
+        <v>72.8</v>
+      </c>
+      <c r="F294" s="11">
+        <v>72.8</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A295" s="10">
+        <v>3</v>
+      </c>
+      <c r="B295" s="10">
+        <f t="shared" si="2"/>
+        <v>92</v>
+      </c>
+      <c r="C295" s="10">
+        <f t="shared" si="2"/>
+        <v>9200</v>
+      </c>
+      <c r="D295" s="11">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="E295" s="11">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="F295" s="11">
+        <v>73.599999999999994</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A296" s="10">
+        <v>3</v>
+      </c>
+      <c r="B296" s="10">
+        <f t="shared" si="2"/>
+        <v>93</v>
+      </c>
+      <c r="C296" s="10">
+        <f t="shared" si="2"/>
+        <v>9300</v>
+      </c>
+      <c r="D296" s="11">
+        <v>74.400000000000006</v>
+      </c>
+      <c r="E296" s="11">
+        <v>74.400000000000006</v>
+      </c>
+      <c r="F296" s="11">
+        <v>74.400000000000006</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A297" s="10">
+        <v>3</v>
+      </c>
+      <c r="B297" s="10">
+        <f t="shared" ref="B297:C303" si="3">B197</f>
+        <v>94</v>
+      </c>
+      <c r="C297" s="10">
+        <f t="shared" si="3"/>
+        <v>9400</v>
+      </c>
+      <c r="D297" s="11">
+        <v>75.2</v>
+      </c>
+      <c r="E297" s="11">
+        <v>75.2</v>
+      </c>
+      <c r="F297" s="11">
+        <v>75.2</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A298" s="10">
+        <v>3</v>
+      </c>
+      <c r="B298" s="10">
+        <f t="shared" si="3"/>
+        <v>95</v>
+      </c>
+      <c r="C298" s="10">
+        <f t="shared" si="3"/>
+        <v>9500</v>
+      </c>
+      <c r="D298" s="11">
+        <v>76</v>
+      </c>
+      <c r="E298" s="11">
+        <v>76</v>
+      </c>
+      <c r="F298" s="11">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A299" s="10">
+        <v>3</v>
+      </c>
+      <c r="B299" s="10">
+        <f t="shared" si="3"/>
+        <v>96</v>
+      </c>
+      <c r="C299" s="10">
+        <f t="shared" si="3"/>
+        <v>9600</v>
+      </c>
+      <c r="D299" s="11">
+        <v>76.8</v>
+      </c>
+      <c r="E299" s="11">
+        <v>76.8</v>
+      </c>
+      <c r="F299" s="11">
+        <v>76.8</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A300" s="10">
+        <v>3</v>
+      </c>
+      <c r="B300" s="10">
+        <f t="shared" si="3"/>
+        <v>97</v>
+      </c>
+      <c r="C300" s="10">
+        <f t="shared" si="3"/>
+        <v>9700</v>
+      </c>
+      <c r="D300" s="11">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="E300" s="11">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="F300" s="11">
+        <v>77.599999999999994</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A301" s="10">
+        <v>3</v>
+      </c>
+      <c r="B301" s="10">
+        <f t="shared" si="3"/>
+        <v>98</v>
+      </c>
+      <c r="C301" s="10">
+        <f t="shared" si="3"/>
+        <v>9800</v>
+      </c>
+      <c r="D301" s="11">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="E301" s="11">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="F301" s="11">
+        <v>78.400000000000006</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A302" s="10">
+        <v>3</v>
+      </c>
+      <c r="B302" s="10">
+        <f t="shared" si="3"/>
+        <v>99</v>
+      </c>
+      <c r="C302" s="10">
+        <f t="shared" si="3"/>
+        <v>9900</v>
+      </c>
+      <c r="D302" s="11">
+        <v>79.2</v>
+      </c>
+      <c r="E302" s="11">
+        <v>79.2</v>
+      </c>
+      <c r="F302" s="11">
+        <v>79.2</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A303" s="10">
+        <v>3</v>
+      </c>
+      <c r="B303" s="10">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="C303" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D303" s="11">
+        <v>80</v>
+      </c>
+      <c r="E303" s="11">
+        <v>80</v>
+      </c>
+      <c r="F303" s="11">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BC725E4-6C6D-4680-9425-DA4423D7A6EF}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="11" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="25" width="17.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <f>B4*(C4-1)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <f t="shared" ref="D5:D6" si="0">B5*(C5-1)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E51963-231E-443F-8008-D46429424FA2}">
+  <dimension ref="A1:Q27"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.625" customWidth="1"/>
+    <col min="3" max="3" width="12.125" customWidth="1"/>
+    <col min="4" max="4" width="11.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="13">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>60</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <f>D4</f>
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>25</v>
+      </c>
+      <c r="G4">
+        <v>8</v>
+      </c>
+      <c r="H4">
+        <f>G4</f>
+        <v>8</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <f>J4</f>
+        <v>12</v>
+      </c>
+      <c r="L4">
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>15</v>
+      </c>
+      <c r="N4">
+        <f>M4</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="13">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>60</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <f t="shared" ref="E5:E27" si="0">D5</f>
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <f t="shared" ref="H5:H27" si="1">G5</f>
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <f t="shared" ref="K5:K27" si="2">J5</f>
+        <v>12</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>15</v>
+      </c>
+      <c r="N5">
+        <f t="shared" ref="N5:N27" si="3">M5</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="13">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>60</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>25</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>15</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="13">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>60</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>25</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="13">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>60</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>25</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <v>12</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L8">
+        <v>5</v>
+      </c>
+      <c r="M8">
+        <v>15</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="13">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>60</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>25</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <v>12</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L9">
+        <v>5</v>
+      </c>
+      <c r="M9">
+        <v>15</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="13">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>60</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F10">
+        <v>25</v>
+      </c>
+      <c r="G10">
+        <v>8</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I10">
+        <v>10</v>
+      </c>
+      <c r="J10">
+        <v>12</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L10">
+        <v>5</v>
+      </c>
+      <c r="M10">
+        <v>15</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="13">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>60</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>8</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11">
+        <v>12</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L11">
+        <v>5</v>
+      </c>
+      <c r="M11">
+        <v>15</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="13">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>60</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F12">
+        <v>25</v>
+      </c>
+      <c r="G12">
+        <v>8</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I12">
+        <v>10</v>
+      </c>
+      <c r="J12">
+        <v>12</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L12">
+        <v>5</v>
+      </c>
+      <c r="M12">
+        <v>15</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="13">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>60</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F13">
+        <v>25</v>
+      </c>
+      <c r="G13">
+        <v>8</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+      <c r="J13">
+        <v>12</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L13">
+        <v>5</v>
+      </c>
+      <c r="M13">
+        <v>15</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="str">
+        <f>"Anti"&amp;A8</f>
+        <v>AntiCritRate</v>
+      </c>
+      <c r="B14" s="13">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>60</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F14">
+        <v>25</v>
+      </c>
+      <c r="G14">
+        <v>8</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I14">
+        <v>10</v>
+      </c>
+      <c r="J14">
+        <v>12</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L14">
+        <v>5</v>
+      </c>
+      <c r="M14">
+        <v>15</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="str">
+        <f t="shared" ref="A15:A19" si="4">"Anti"&amp;A9</f>
+        <v>AntiCounterRate</v>
+      </c>
+      <c r="B15" s="13">
+        <v>10</v>
+      </c>
+      <c r="C15">
+        <v>60</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F15">
+        <v>25</v>
+      </c>
+      <c r="G15">
+        <v>8</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I15">
+        <v>10</v>
+      </c>
+      <c r="J15">
+        <v>12</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L15">
+        <v>5</v>
+      </c>
+      <c r="M15">
+        <v>15</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>AntiComboRate</v>
+      </c>
+      <c r="B16" s="13">
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <v>60</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F16">
+        <v>25</v>
+      </c>
+      <c r="G16">
+        <v>8</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I16">
+        <v>10</v>
+      </c>
+      <c r="J16">
+        <v>12</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L16">
+        <v>5</v>
+      </c>
+      <c r="M16">
+        <v>15</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>AntiDodgeRate</v>
+      </c>
+      <c r="B17" s="13">
+        <v>10</v>
+      </c>
+      <c r="C17">
+        <v>60</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F17">
+        <v>25</v>
+      </c>
+      <c r="G17">
+        <v>8</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I17">
+        <v>10</v>
+      </c>
+      <c r="J17">
+        <v>12</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L17">
+        <v>5</v>
+      </c>
+      <c r="M17">
+        <v>15</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>AntiStunRate</v>
+      </c>
+      <c r="B18" s="13">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>60</v>
+      </c>
+      <c r="D18">
+        <v>5</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F18">
+        <v>25</v>
+      </c>
+      <c r="G18">
+        <v>8</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I18">
+        <v>10</v>
+      </c>
+      <c r="J18">
+        <v>12</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L18">
+        <v>5</v>
+      </c>
+      <c r="M18">
+        <v>15</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>AntiLifeStealRate</v>
+      </c>
+      <c r="B19" s="13">
+        <v>10</v>
+      </c>
+      <c r="C19">
+        <v>60</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F19">
+        <v>25</v>
+      </c>
+      <c r="G19">
+        <v>8</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I19">
+        <v>10</v>
+      </c>
+      <c r="J19">
+        <v>12</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L19">
+        <v>5</v>
+      </c>
+      <c r="M19">
+        <v>15</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="13">
+        <v>10</v>
+      </c>
+      <c r="C20">
+        <v>60</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F20">
+        <v>25</v>
+      </c>
+      <c r="G20">
+        <v>8</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I20">
+        <v>10</v>
+      </c>
+      <c r="J20">
+        <v>12</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L20">
+        <v>5</v>
+      </c>
+      <c r="M20">
+        <v>15</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="str">
+        <f>"Anti"&amp;A20</f>
+        <v>AntiCritDmg</v>
+      </c>
+      <c r="B21" s="13">
+        <v>10</v>
+      </c>
+      <c r="C21">
+        <v>60</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F21">
+        <v>25</v>
+      </c>
+      <c r="G21">
+        <v>8</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I21">
+        <v>10</v>
+      </c>
+      <c r="J21">
+        <v>12</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L21">
+        <v>5</v>
+      </c>
+      <c r="M21">
+        <v>15</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="13">
+        <v>10</v>
+      </c>
+      <c r="C22">
+        <v>60</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F22">
+        <v>25</v>
+      </c>
+      <c r="G22">
+        <v>8</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I22">
+        <v>10</v>
+      </c>
+      <c r="J22">
+        <v>12</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L22">
+        <v>5</v>
+      </c>
+      <c r="M22">
+        <v>15</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="13">
+        <v>10</v>
+      </c>
+      <c r="C23">
+        <v>60</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F23">
+        <v>25</v>
+      </c>
+      <c r="G23">
+        <v>8</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I23">
+        <v>10</v>
+      </c>
+      <c r="J23">
+        <v>12</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L23">
+        <v>5</v>
+      </c>
+      <c r="M23">
+        <v>15</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="13">
+        <v>10</v>
+      </c>
+      <c r="C24">
+        <v>60</v>
+      </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F24">
+        <v>25</v>
+      </c>
+      <c r="G24">
+        <v>8</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I24">
+        <v>10</v>
+      </c>
+      <c r="J24">
+        <v>12</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L24">
+        <v>5</v>
+      </c>
+      <c r="M24">
+        <v>15</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="13">
+        <v>10</v>
+      </c>
+      <c r="C25">
+        <v>60</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F25">
+        <v>25</v>
+      </c>
+      <c r="G25">
+        <v>8</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I25">
+        <v>10</v>
+      </c>
+      <c r="J25">
+        <v>12</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L25">
+        <v>5</v>
+      </c>
+      <c r="M25">
+        <v>15</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="13">
+        <v>10</v>
+      </c>
+      <c r="C26">
+        <v>60</v>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F26">
+        <v>25</v>
+      </c>
+      <c r="G26">
+        <v>8</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I26">
+        <v>10</v>
+      </c>
+      <c r="J26">
+        <v>12</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L26">
+        <v>5</v>
+      </c>
+      <c r="M26">
+        <v>15</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="13">
+        <v>10</v>
+      </c>
+      <c r="C27">
+        <v>60</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F27">
+        <v>25</v>
+      </c>
+      <c r="G27">
+        <v>8</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I27">
+        <v>10</v>
+      </c>
+      <c r="J27">
+        <v>12</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="L27">
+        <v>5</v>
+      </c>
+      <c r="M27">
+        <v>15</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>

--- a/Assets/Excel/Pets.xlsx
+++ b/Assets/Excel/Pets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEB483C-4892-4788-AD27-09D236555C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A77B198-EB06-48A0-9E7C-2F076C0A44E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pets" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="152">
   <si>
     <t>String</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -493,6 +493,110 @@
   </si>
   <si>
     <t>FoodReturn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敏捷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪避</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>击晕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵抗暴击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵抗反击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵抗连击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵抗闪避</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵抗击晕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵抗吸血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化爆伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱化爆伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最终增伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最终减伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化治疗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱化治疗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化宠物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱化宠物</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -891,25 +995,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E113BB45-2004-4A47-8070-A66C92D5B66E}">
   <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="10.75" style="2" customWidth="1"/>
-    <col min="4" max="4" width="9.58203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="41.375" style="2" customWidth="1"/>
     <col min="7" max="7" width="12.25" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.25" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.5" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.58203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.625" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.75" style="2" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.58203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.625" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -953,7 +1057,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -997,7 +1101,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -1041,7 +1145,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>101</v>
       </c>
@@ -1085,7 +1189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>102</v>
       </c>
@@ -1129,7 +1233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>103</v>
       </c>
@@ -1194,18 +1298,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E76EACD-2167-4635-97EC-A76DDB474FD3}">
   <dimension ref="A1:H303"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" customWidth="1"/>
-    <col min="2" max="2" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.08203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>74</v>
       </c>
@@ -1228,7 +1332,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>14</v>
       </c>
@@ -1251,7 +1355,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>76</v>
       </c>
@@ -1274,7 +1378,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
         <v>1</v>
       </c>
@@ -1301,7 +1405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>1</v>
       </c>
@@ -1329,7 +1433,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
         <v>1</v>
       </c>
@@ -1357,7 +1461,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
         <v>1</v>
       </c>
@@ -1385,7 +1489,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
         <v>1</v>
       </c>
@@ -1413,7 +1517,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <v>1</v>
       </c>
@@ -1441,7 +1545,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <v>1</v>
       </c>
@@ -1469,7 +1573,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
         <v>1</v>
       </c>
@@ -1497,7 +1601,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
         <v>1</v>
       </c>
@@ -1525,7 +1629,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
         <v>1</v>
       </c>
@@ -1553,7 +1657,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="9">
         <v>1</v>
       </c>
@@ -1581,7 +1685,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
         <v>1</v>
       </c>
@@ -1609,7 +1713,7 @@
         <v>6600</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="9">
         <v>1</v>
       </c>
@@ -1637,7 +1741,7 @@
         <v>7800</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
         <v>1</v>
       </c>
@@ -1665,7 +1769,7 @@
         <v>9100</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
         <v>1</v>
       </c>
@@ -1693,7 +1797,7 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
         <v>1</v>
       </c>
@@ -1721,7 +1825,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
         <v>1</v>
       </c>
@@ -1749,7 +1853,7 @@
         <v>13600</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <v>1</v>
       </c>
@@ -1777,7 +1881,7 @@
         <v>15300</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
         <v>1</v>
       </c>
@@ -1805,7 +1909,7 @@
         <v>17100</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
         <v>1</v>
       </c>
@@ -1833,7 +1937,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
         <v>1</v>
       </c>
@@ -1861,7 +1965,7 @@
         <v>21000</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
         <v>1</v>
       </c>
@@ -1889,7 +1993,7 @@
         <v>23100</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
         <v>1</v>
       </c>
@@ -1917,7 +2021,7 @@
         <v>25300</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
         <v>1</v>
       </c>
@@ -1945,7 +2049,7 @@
         <v>27600</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
         <v>1</v>
       </c>
@@ -1973,7 +2077,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
         <v>1</v>
       </c>
@@ -2001,7 +2105,7 @@
         <v>32500</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
         <v>1</v>
       </c>
@@ -2029,7 +2133,7 @@
         <v>35100</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
         <v>1</v>
       </c>
@@ -2057,7 +2161,7 @@
         <v>37800</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
         <v>1</v>
       </c>
@@ -2085,7 +2189,7 @@
         <v>40600</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
         <v>1</v>
       </c>
@@ -2113,7 +2217,7 @@
         <v>43500</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
         <v>1</v>
       </c>
@@ -2141,7 +2245,7 @@
         <v>46500</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
         <v>1</v>
       </c>
@@ -2169,7 +2273,7 @@
         <v>49600</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
         <v>1</v>
       </c>
@@ -2197,7 +2301,7 @@
         <v>52800</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
         <v>1</v>
       </c>
@@ -2225,7 +2329,7 @@
         <v>56100</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="9">
         <v>1</v>
       </c>
@@ -2253,7 +2357,7 @@
         <v>59500</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <v>1</v>
       </c>
@@ -2281,7 +2385,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
         <v>1</v>
       </c>
@@ -2309,7 +2413,7 @@
         <v>66600</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <v>1</v>
       </c>
@@ -2337,7 +2441,7 @@
         <v>70300</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
         <v>1</v>
       </c>
@@ -2365,7 +2469,7 @@
         <v>74100</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <v>1</v>
       </c>
@@ -2393,7 +2497,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <v>1</v>
       </c>
@@ -2421,7 +2525,7 @@
         <v>82000</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <v>1</v>
       </c>
@@ -2449,7 +2553,7 @@
         <v>86100</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
         <v>1</v>
       </c>
@@ -2477,7 +2581,7 @@
         <v>90300</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <v>1</v>
       </c>
@@ -2505,7 +2609,7 @@
         <v>94600</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="9">
         <v>1</v>
       </c>
@@ -2533,7 +2637,7 @@
         <v>99000</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="9">
         <v>1</v>
       </c>
@@ -2561,7 +2665,7 @@
         <v>103500</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
         <v>1</v>
       </c>
@@ -2589,7 +2693,7 @@
         <v>108100</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <v>1</v>
       </c>
@@ -2617,7 +2721,7 @@
         <v>112800</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="9">
         <v>1</v>
       </c>
@@ -2645,7 +2749,7 @@
         <v>117600</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="9">
         <v>1</v>
       </c>
@@ -2673,7 +2777,7 @@
         <v>122500</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="9">
         <v>1</v>
       </c>
@@ -2701,7 +2805,7 @@
         <v>127500</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="9">
         <v>1</v>
       </c>
@@ -2729,7 +2833,7 @@
         <v>132600</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="9">
         <v>1</v>
       </c>
@@ -2757,7 +2861,7 @@
         <v>137800</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="9">
         <v>1</v>
       </c>
@@ -2785,7 +2889,7 @@
         <v>143100</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="9">
         <v>1</v>
       </c>
@@ -2813,7 +2917,7 @@
         <v>148500</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="9">
         <v>1</v>
       </c>
@@ -2841,7 +2945,7 @@
         <v>154000</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="9">
         <v>1</v>
       </c>
@@ -2869,7 +2973,7 @@
         <v>159600</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="9">
         <v>1</v>
       </c>
@@ -2897,7 +3001,7 @@
         <v>165300</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="9">
         <v>1</v>
       </c>
@@ -2925,7 +3029,7 @@
         <v>171100</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="9">
         <v>1</v>
       </c>
@@ -2953,7 +3057,7 @@
         <v>177000</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="9">
         <v>1</v>
       </c>
@@ -2981,7 +3085,7 @@
         <v>183000</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="9">
         <v>1</v>
       </c>
@@ -3009,7 +3113,7 @@
         <v>189100</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="9">
         <v>1</v>
       </c>
@@ -3037,7 +3141,7 @@
         <v>195300</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="9">
         <v>1</v>
       </c>
@@ -3065,7 +3169,7 @@
         <v>201600</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="9">
         <v>1</v>
       </c>
@@ -3093,7 +3197,7 @@
         <v>208000</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="9">
         <v>1</v>
       </c>
@@ -3121,7 +3225,7 @@
         <v>214500</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="9">
         <v>1</v>
       </c>
@@ -3149,7 +3253,7 @@
         <v>221100</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="9">
         <v>1</v>
       </c>
@@ -3177,7 +3281,7 @@
         <v>227800</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="9">
         <v>1</v>
       </c>
@@ -3205,7 +3309,7 @@
         <v>234600</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="9">
         <v>1</v>
       </c>
@@ -3233,7 +3337,7 @@
         <v>241500</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="9">
         <v>1</v>
       </c>
@@ -3261,7 +3365,7 @@
         <v>248500</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="9">
         <v>1</v>
       </c>
@@ -3289,7 +3393,7 @@
         <v>255600</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="9">
         <v>1</v>
       </c>
@@ -3317,7 +3421,7 @@
         <v>262800</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="9">
         <v>1</v>
       </c>
@@ -3345,7 +3449,7 @@
         <v>270100</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="9">
         <v>1</v>
       </c>
@@ -3373,7 +3477,7 @@
         <v>277500</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="9">
         <v>1</v>
       </c>
@@ -3401,7 +3505,7 @@
         <v>285000</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="9">
         <v>1</v>
       </c>
@@ -3429,7 +3533,7 @@
         <v>292600</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="9">
         <v>1</v>
       </c>
@@ -3457,7 +3561,7 @@
         <v>300300</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="9">
         <v>1</v>
       </c>
@@ -3485,7 +3589,7 @@
         <v>308100</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="9">
         <v>1</v>
       </c>
@@ -3513,7 +3617,7 @@
         <v>316000</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="9">
         <v>1</v>
       </c>
@@ -3541,7 +3645,7 @@
         <v>324000</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="9">
         <v>1</v>
       </c>
@@ -3569,7 +3673,7 @@
         <v>332100</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="9">
         <v>1</v>
       </c>
@@ -3597,7 +3701,7 @@
         <v>340300</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="9">
         <v>1</v>
       </c>
@@ -3625,7 +3729,7 @@
         <v>348600</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="9">
         <v>1</v>
       </c>
@@ -3653,7 +3757,7 @@
         <v>357000</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="9">
         <v>1</v>
       </c>
@@ -3681,7 +3785,7 @@
         <v>365500</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="9">
         <v>1</v>
       </c>
@@ -3709,7 +3813,7 @@
         <v>374100</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="9">
         <v>1</v>
       </c>
@@ -3737,7 +3841,7 @@
         <v>382800</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="9">
         <v>1</v>
       </c>
@@ -3765,7 +3869,7 @@
         <v>391600</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="9">
         <v>1</v>
       </c>
@@ -3793,7 +3897,7 @@
         <v>400500</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="9">
         <v>1</v>
       </c>
@@ -3821,7 +3925,7 @@
         <v>409500</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="9">
         <v>1</v>
       </c>
@@ -3849,7 +3953,7 @@
         <v>418600</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="9">
         <v>1</v>
       </c>
@@ -3877,7 +3981,7 @@
         <v>427800</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="9">
         <v>1</v>
       </c>
@@ -3905,7 +4009,7 @@
         <v>437100</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="9">
         <v>1</v>
       </c>
@@ -3933,7 +4037,7 @@
         <v>446500</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="9">
         <v>1</v>
       </c>
@@ -3961,7 +4065,7 @@
         <v>456000</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="9">
         <v>1</v>
       </c>
@@ -3989,7 +4093,7 @@
         <v>465600</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="9">
         <v>1</v>
       </c>
@@ -4017,7 +4121,7 @@
         <v>475300</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="9">
         <v>1</v>
       </c>
@@ -4045,7 +4149,7 @@
         <v>485100</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="9">
         <v>1</v>
       </c>
@@ -4073,7 +4177,7 @@
         <v>495000</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="9">
         <v>2</v>
       </c>
@@ -4103,7 +4207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="9">
         <v>2</v>
       </c>
@@ -4133,7 +4237,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="9">
         <v>2</v>
       </c>
@@ -4163,7 +4267,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="9">
         <v>2</v>
       </c>
@@ -4193,7 +4297,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="9">
         <v>2</v>
       </c>
@@ -4223,7 +4327,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="9">
         <v>2</v>
       </c>
@@ -4253,7 +4357,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="9">
         <v>2</v>
       </c>
@@ -4283,7 +4387,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="9">
         <v>2</v>
       </c>
@@ -4313,7 +4417,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="9">
         <v>2</v>
       </c>
@@ -4343,7 +4447,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="9">
         <v>2</v>
       </c>
@@ -4373,7 +4477,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="9">
         <v>2</v>
       </c>
@@ -4403,7 +4507,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="9">
         <v>2</v>
       </c>
@@ -4433,7 +4537,7 @@
         <v>6600</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="9">
         <v>2</v>
       </c>
@@ -4463,7 +4567,7 @@
         <v>7800</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="9">
         <v>2</v>
       </c>
@@ -4493,7 +4597,7 @@
         <v>9100</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="9">
         <v>2</v>
       </c>
@@ -4523,7 +4627,7 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="9">
         <v>2</v>
       </c>
@@ -4553,7 +4657,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="9">
         <v>2</v>
       </c>
@@ -4583,7 +4687,7 @@
         <v>13600</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="9">
         <v>2</v>
       </c>
@@ -4613,7 +4717,7 @@
         <v>15300</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="9">
         <v>2</v>
       </c>
@@ -4643,7 +4747,7 @@
         <v>17100</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="9">
         <v>2</v>
       </c>
@@ -4673,7 +4777,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="9">
         <v>2</v>
       </c>
@@ -4703,7 +4807,7 @@
         <v>21000</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="9">
         <v>2</v>
       </c>
@@ -4733,7 +4837,7 @@
         <v>23100</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="9">
         <v>2</v>
       </c>
@@ -4763,7 +4867,7 @@
         <v>25300</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="9">
         <v>2</v>
       </c>
@@ -4793,7 +4897,7 @@
         <v>27600</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="9">
         <v>2</v>
       </c>
@@ -4823,7 +4927,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="9">
         <v>2</v>
       </c>
@@ -4853,7 +4957,7 @@
         <v>32500</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="9">
         <v>2</v>
       </c>
@@ -4883,7 +4987,7 @@
         <v>35100</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="9">
         <v>2</v>
       </c>
@@ -4913,7 +5017,7 @@
         <v>37800</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="9">
         <v>2</v>
       </c>
@@ -4943,7 +5047,7 @@
         <v>40600</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="9">
         <v>2</v>
       </c>
@@ -4973,7 +5077,7 @@
         <v>43500</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="9">
         <v>2</v>
       </c>
@@ -5003,7 +5107,7 @@
         <v>46500</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="9">
         <v>2</v>
       </c>
@@ -5033,7 +5137,7 @@
         <v>49600</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="9">
         <v>2</v>
       </c>
@@ -5063,7 +5167,7 @@
         <v>52800</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="9">
         <v>2</v>
       </c>
@@ -5093,7 +5197,7 @@
         <v>56100</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="9">
         <v>2</v>
       </c>
@@ -5123,7 +5227,7 @@
         <v>59500</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="9">
         <v>2</v>
       </c>
@@ -5153,7 +5257,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="9">
         <v>2</v>
       </c>
@@ -5183,7 +5287,7 @@
         <v>66600</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="9">
         <v>2</v>
       </c>
@@ -5213,7 +5317,7 @@
         <v>70300</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="9">
         <v>2</v>
       </c>
@@ -5243,7 +5347,7 @@
         <v>74100</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="9">
         <v>2</v>
       </c>
@@ -5273,7 +5377,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="9">
         <v>2</v>
       </c>
@@ -5303,7 +5407,7 @@
         <v>82000</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="9">
         <v>2</v>
       </c>
@@ -5333,7 +5437,7 @@
         <v>86100</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="9">
         <v>2</v>
       </c>
@@ -5363,7 +5467,7 @@
         <v>90300</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="9">
         <v>2</v>
       </c>
@@ -5393,7 +5497,7 @@
         <v>94600</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="9">
         <v>2</v>
       </c>
@@ -5423,7 +5527,7 @@
         <v>99000</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="9">
         <v>2</v>
       </c>
@@ -5453,7 +5557,7 @@
         <v>103500</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="9">
         <v>2</v>
       </c>
@@ -5483,7 +5587,7 @@
         <v>108100</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="9">
         <v>2</v>
       </c>
@@ -5513,7 +5617,7 @@
         <v>112800</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="9">
         <v>2</v>
       </c>
@@ -5543,7 +5647,7 @@
         <v>117600</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="9">
         <v>2</v>
       </c>
@@ -5573,7 +5677,7 @@
         <v>122500</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="9">
         <v>2</v>
       </c>
@@ -5603,7 +5707,7 @@
         <v>127500</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="9">
         <v>2</v>
       </c>
@@ -5633,7 +5737,7 @@
         <v>132600</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="9">
         <v>2</v>
       </c>
@@ -5663,7 +5767,7 @@
         <v>137800</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="9">
         <v>2</v>
       </c>
@@ -5693,7 +5797,7 @@
         <v>143100</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="9">
         <v>2</v>
       </c>
@@ -5723,7 +5827,7 @@
         <v>148500</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="9">
         <v>2</v>
       </c>
@@ -5753,7 +5857,7 @@
         <v>154000</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="9">
         <v>2</v>
       </c>
@@ -5783,7 +5887,7 @@
         <v>159600</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="9">
         <v>2</v>
       </c>
@@ -5813,7 +5917,7 @@
         <v>165300</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="9">
         <v>2</v>
       </c>
@@ -5843,7 +5947,7 @@
         <v>171100</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="9">
         <v>2</v>
       </c>
@@ -5873,7 +5977,7 @@
         <v>177000</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="9">
         <v>2</v>
       </c>
@@ -5903,7 +6007,7 @@
         <v>183000</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="9">
         <v>2</v>
       </c>
@@ -5933,7 +6037,7 @@
         <v>189100</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="9">
         <v>2</v>
       </c>
@@ -5963,7 +6067,7 @@
         <v>195300</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="9">
         <v>2</v>
       </c>
@@ -5993,7 +6097,7 @@
         <v>201600</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="9">
         <v>2</v>
       </c>
@@ -6023,7 +6127,7 @@
         <v>208000</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="9">
         <v>2</v>
       </c>
@@ -6053,7 +6157,7 @@
         <v>214500</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="9">
         <v>2</v>
       </c>
@@ -6083,7 +6187,7 @@
         <v>221100</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="9">
         <v>2</v>
       </c>
@@ -6113,7 +6217,7 @@
         <v>227800</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="9">
         <v>2</v>
       </c>
@@ -6143,7 +6247,7 @@
         <v>234600</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="9">
         <v>2</v>
       </c>
@@ -6173,7 +6277,7 @@
         <v>241500</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="9">
         <v>2</v>
       </c>
@@ -6203,7 +6307,7 @@
         <v>248500</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="9">
         <v>2</v>
       </c>
@@ -6233,7 +6337,7 @@
         <v>255600</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="9">
         <v>2</v>
       </c>
@@ -6263,7 +6367,7 @@
         <v>262800</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="9">
         <v>2</v>
       </c>
@@ -6293,7 +6397,7 @@
         <v>270100</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="9">
         <v>2</v>
       </c>
@@ -6323,7 +6427,7 @@
         <v>277500</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="9">
         <v>2</v>
       </c>
@@ -6353,7 +6457,7 @@
         <v>285000</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="9">
         <v>2</v>
       </c>
@@ -6383,7 +6487,7 @@
         <v>292600</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="9">
         <v>2</v>
       </c>
@@ -6413,7 +6517,7 @@
         <v>300300</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="9">
         <v>2</v>
       </c>
@@ -6443,7 +6547,7 @@
         <v>308100</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="9">
         <v>2</v>
       </c>
@@ -6473,7 +6577,7 @@
         <v>316000</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="9">
         <v>2</v>
       </c>
@@ -6503,7 +6607,7 @@
         <v>324000</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="9">
         <v>2</v>
       </c>
@@ -6533,7 +6637,7 @@
         <v>332100</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="9">
         <v>2</v>
       </c>
@@ -6563,7 +6667,7 @@
         <v>340300</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="9">
         <v>2</v>
       </c>
@@ -6593,7 +6697,7 @@
         <v>348600</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="9">
         <v>2</v>
       </c>
@@ -6623,7 +6727,7 @@
         <v>357000</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="9">
         <v>2</v>
       </c>
@@ -6653,7 +6757,7 @@
         <v>365500</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="9">
         <v>2</v>
       </c>
@@ -6683,7 +6787,7 @@
         <v>374100</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="9">
         <v>2</v>
       </c>
@@ -6713,7 +6817,7 @@
         <v>382800</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="9">
         <v>2</v>
       </c>
@@ -6743,7 +6847,7 @@
         <v>391600</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="9">
         <v>2</v>
       </c>
@@ -6773,7 +6877,7 @@
         <v>400500</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="9">
         <v>2</v>
       </c>
@@ -6803,7 +6907,7 @@
         <v>409500</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="9">
         <v>2</v>
       </c>
@@ -6833,7 +6937,7 @@
         <v>418600</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="9">
         <v>2</v>
       </c>
@@ -6863,7 +6967,7 @@
         <v>427800</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="9">
         <v>2</v>
       </c>
@@ -6893,7 +6997,7 @@
         <v>437100</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="9">
         <v>2</v>
       </c>
@@ -6923,7 +7027,7 @@
         <v>446500</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="9">
         <v>2</v>
       </c>
@@ -6953,7 +7057,7 @@
         <v>456000</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="9">
         <v>2</v>
       </c>
@@ -6983,7 +7087,7 @@
         <v>465600</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="9">
         <v>2</v>
       </c>
@@ -7013,7 +7117,7 @@
         <v>475300</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="9">
         <v>2</v>
       </c>
@@ -7043,7 +7147,7 @@
         <v>485100</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="9">
         <v>2</v>
       </c>
@@ -7073,7 +7177,7 @@
         <v>495000</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="9">
         <v>3</v>
       </c>
@@ -7103,7 +7207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="9">
         <v>3</v>
       </c>
@@ -7133,7 +7237,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="9">
         <v>3</v>
       </c>
@@ -7163,7 +7267,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="9">
         <v>3</v>
       </c>
@@ -7193,7 +7297,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="9">
         <v>3</v>
       </c>
@@ -7223,7 +7327,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="9">
         <v>3</v>
       </c>
@@ -7253,7 +7357,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="9">
         <v>3</v>
       </c>
@@ -7283,7 +7387,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="9">
         <v>3</v>
       </c>
@@ -7313,7 +7417,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="9">
         <v>3</v>
       </c>
@@ -7343,7 +7447,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="9">
         <v>3</v>
       </c>
@@ -7373,7 +7477,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="9">
         <v>3</v>
       </c>
@@ -7403,7 +7507,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="9">
         <v>3</v>
       </c>
@@ -7433,7 +7537,7 @@
         <v>6600</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="9">
         <v>3</v>
       </c>
@@ -7463,7 +7567,7 @@
         <v>7800</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="9">
         <v>3</v>
       </c>
@@ -7493,7 +7597,7 @@
         <v>9100</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="9">
         <v>3</v>
       </c>
@@ -7523,7 +7627,7 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="9">
         <v>3</v>
       </c>
@@ -7553,7 +7657,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="9">
         <v>3</v>
       </c>
@@ -7583,7 +7687,7 @@
         <v>13600</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="9">
         <v>3</v>
       </c>
@@ -7613,7 +7717,7 @@
         <v>15300</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="9">
         <v>3</v>
       </c>
@@ -7643,7 +7747,7 @@
         <v>17100</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="9">
         <v>3</v>
       </c>
@@ -7673,7 +7777,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="9">
         <v>3</v>
       </c>
@@ -7703,7 +7807,7 @@
         <v>21000</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="9">
         <v>3</v>
       </c>
@@ -7733,7 +7837,7 @@
         <v>23100</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="9">
         <v>3</v>
       </c>
@@ -7763,7 +7867,7 @@
         <v>25300</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="9">
         <v>3</v>
       </c>
@@ -7793,7 +7897,7 @@
         <v>27600</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="9">
         <v>3</v>
       </c>
@@ -7823,7 +7927,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="9">
         <v>3</v>
       </c>
@@ -7853,7 +7957,7 @@
         <v>32500</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="9">
         <v>3</v>
       </c>
@@ -7883,7 +7987,7 @@
         <v>35100</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="9">
         <v>3</v>
       </c>
@@ -7913,7 +8017,7 @@
         <v>37800</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="9">
         <v>3</v>
       </c>
@@ -7943,7 +8047,7 @@
         <v>40600</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="9">
         <v>3</v>
       </c>
@@ -7973,7 +8077,7 @@
         <v>43500</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="9">
         <v>3</v>
       </c>
@@ -8003,7 +8107,7 @@
         <v>46500</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="9">
         <v>3</v>
       </c>
@@ -8033,7 +8137,7 @@
         <v>49600</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="9">
         <v>3</v>
       </c>
@@ -8063,7 +8167,7 @@
         <v>52800</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="9">
         <v>3</v>
       </c>
@@ -8093,7 +8197,7 @@
         <v>56100</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" s="9">
         <v>3</v>
       </c>
@@ -8123,7 +8227,7 @@
         <v>59500</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="9">
         <v>3</v>
       </c>
@@ -8153,7 +8257,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="9">
         <v>3</v>
       </c>
@@ -8183,7 +8287,7 @@
         <v>66600</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="9">
         <v>3</v>
       </c>
@@ -8213,7 +8317,7 @@
         <v>70300</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="9">
         <v>3</v>
       </c>
@@ -8243,7 +8347,7 @@
         <v>74100</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="9">
         <v>3</v>
       </c>
@@ -8273,7 +8377,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="9">
         <v>3</v>
       </c>
@@ -8303,7 +8407,7 @@
         <v>82000</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="9">
         <v>3</v>
       </c>
@@ -8333,7 +8437,7 @@
         <v>86100</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="9">
         <v>3</v>
       </c>
@@ -8363,7 +8467,7 @@
         <v>90300</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="9">
         <v>3</v>
       </c>
@@ -8393,7 +8497,7 @@
         <v>94600</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="9">
         <v>3</v>
       </c>
@@ -8423,7 +8527,7 @@
         <v>99000</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="9">
         <v>3</v>
       </c>
@@ -8453,7 +8557,7 @@
         <v>103500</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="9">
         <v>3</v>
       </c>
@@ -8483,7 +8587,7 @@
         <v>108100</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="9">
         <v>3</v>
       </c>
@@ -8513,7 +8617,7 @@
         <v>112800</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="9">
         <v>3</v>
       </c>
@@ -8543,7 +8647,7 @@
         <v>117600</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="9">
         <v>3</v>
       </c>
@@ -8573,7 +8677,7 @@
         <v>122500</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="9">
         <v>3</v>
       </c>
@@ -8603,7 +8707,7 @@
         <v>127500</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="9">
         <v>3</v>
       </c>
@@ -8633,7 +8737,7 @@
         <v>132600</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="9">
         <v>3</v>
       </c>
@@ -8663,7 +8767,7 @@
         <v>137800</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="9">
         <v>3</v>
       </c>
@@ -8693,7 +8797,7 @@
         <v>143100</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="9">
         <v>3</v>
       </c>
@@ -8723,7 +8827,7 @@
         <v>148500</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="9">
         <v>3</v>
       </c>
@@ -8753,7 +8857,7 @@
         <v>154000</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="9">
         <v>3</v>
       </c>
@@ -8783,7 +8887,7 @@
         <v>159600</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="9">
         <v>3</v>
       </c>
@@ -8813,7 +8917,7 @@
         <v>165300</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="9">
         <v>3</v>
       </c>
@@ -8843,7 +8947,7 @@
         <v>171100</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="9">
         <v>3</v>
       </c>
@@ -8873,7 +8977,7 @@
         <v>177000</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="9">
         <v>3</v>
       </c>
@@ -8903,7 +9007,7 @@
         <v>183000</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="9">
         <v>3</v>
       </c>
@@ -8933,7 +9037,7 @@
         <v>189100</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" s="9">
         <v>3</v>
       </c>
@@ -8963,7 +9067,7 @@
         <v>195300</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" s="9">
         <v>3</v>
       </c>
@@ -8993,7 +9097,7 @@
         <v>201600</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268" s="9">
         <v>3</v>
       </c>
@@ -9023,7 +9127,7 @@
         <v>208000</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A269" s="9">
         <v>3</v>
       </c>
@@ -9053,7 +9157,7 @@
         <v>214500</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270" s="9">
         <v>3</v>
       </c>
@@ -9083,7 +9187,7 @@
         <v>221100</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" s="9">
         <v>3</v>
       </c>
@@ -9113,7 +9217,7 @@
         <v>227800</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" s="9">
         <v>3</v>
       </c>
@@ -9143,7 +9247,7 @@
         <v>234600</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273" s="9">
         <v>3</v>
       </c>
@@ -9173,7 +9277,7 @@
         <v>241500</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274" s="9">
         <v>3</v>
       </c>
@@ -9203,7 +9307,7 @@
         <v>248500</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275" s="9">
         <v>3</v>
       </c>
@@ -9233,7 +9337,7 @@
         <v>255600</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276" s="9">
         <v>3</v>
       </c>
@@ -9263,7 +9367,7 @@
         <v>262800</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277" s="9">
         <v>3</v>
       </c>
@@ -9293,7 +9397,7 @@
         <v>270100</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278" s="9">
         <v>3</v>
       </c>
@@ -9323,7 +9427,7 @@
         <v>277500</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279" s="9">
         <v>3</v>
       </c>
@@ -9353,7 +9457,7 @@
         <v>285000</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A280" s="9">
         <v>3</v>
       </c>
@@ -9383,7 +9487,7 @@
         <v>292600</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281" s="9">
         <v>3</v>
       </c>
@@ -9413,7 +9517,7 @@
         <v>300300</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" s="9">
         <v>3</v>
       </c>
@@ -9443,7 +9547,7 @@
         <v>308100</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283" s="9">
         <v>3</v>
       </c>
@@ -9473,7 +9577,7 @@
         <v>316000</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284" s="9">
         <v>3</v>
       </c>
@@ -9503,7 +9607,7 @@
         <v>324000</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285" s="9">
         <v>3</v>
       </c>
@@ -9533,7 +9637,7 @@
         <v>332100</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286" s="9">
         <v>3</v>
       </c>
@@ -9563,7 +9667,7 @@
         <v>340300</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287" s="9">
         <v>3</v>
       </c>
@@ -9593,7 +9697,7 @@
         <v>348600</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A288" s="9">
         <v>3</v>
       </c>
@@ -9623,7 +9727,7 @@
         <v>357000</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" s="9">
         <v>3</v>
       </c>
@@ -9653,7 +9757,7 @@
         <v>365500</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" s="9">
         <v>3</v>
       </c>
@@ -9683,7 +9787,7 @@
         <v>374100</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" s="9">
         <v>3</v>
       </c>
@@ -9713,7 +9817,7 @@
         <v>382800</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" s="9">
         <v>3</v>
       </c>
@@ -9743,7 +9847,7 @@
         <v>391600</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A293" s="9">
         <v>3</v>
       </c>
@@ -9773,7 +9877,7 @@
         <v>400500</v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A294" s="9">
         <v>3</v>
       </c>
@@ -9803,7 +9907,7 @@
         <v>409500</v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A295" s="9">
         <v>3</v>
       </c>
@@ -9833,7 +9937,7 @@
         <v>418600</v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A296" s="9">
         <v>3</v>
       </c>
@@ -9863,7 +9967,7 @@
         <v>427800</v>
       </c>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A297" s="9">
         <v>3</v>
       </c>
@@ -9893,7 +9997,7 @@
         <v>437100</v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A298" s="9">
         <v>3</v>
       </c>
@@ -9923,7 +10027,7 @@
         <v>446500</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A299" s="9">
         <v>3</v>
       </c>
@@ -9953,7 +10057,7 @@
         <v>456000</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A300" s="9">
         <v>3</v>
       </c>
@@ -9983,7 +10087,7 @@
         <v>465600</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A301" s="9">
         <v>3</v>
       </c>
@@ -10013,7 +10117,7 @@
         <v>475300</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A302" s="9">
         <v>3</v>
       </c>
@@ -10043,7 +10147,7 @@
         <v>485100</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A303" s="9">
         <v>3</v>
       </c>
@@ -10082,16 +10186,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BC725E4-6C6D-4680-9425-DA4423D7A6EF}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.08203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.125" bestFit="1" customWidth="1"/>
     <col min="5" max="11" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="25" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="25" width="17.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>74</v>
       </c>
@@ -10105,7 +10209,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>36</v>
       </c>
@@ -10119,7 +10223,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>75</v>
       </c>
@@ -10133,7 +10237,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -10148,7 +10252,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
@@ -10163,7 +10267,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3</v>
       </c>
@@ -10187,9 +10291,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF11992-3A8B-41E6-B69C-887C929CEC0B}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>114</v>
       </c>
@@ -10197,7 +10301,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>36</v>
       </c>
@@ -10205,7 +10309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>115</v>
       </c>
@@ -10213,7 +10317,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -10221,7 +10325,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
@@ -10229,7 +10333,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3</v>
       </c>
@@ -10237,7 +10341,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>4</v>
       </c>
@@ -10245,7 +10349,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>5</v>
       </c>
@@ -10253,7 +10357,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>6</v>
       </c>
@@ -10261,7 +10365,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>7</v>
       </c>
@@ -10269,7 +10373,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>8</v>
       </c>
@@ -10277,7 +10381,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>9</v>
       </c>
@@ -10285,7 +10389,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>10</v>
       </c>
@@ -10293,7 +10397,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>11</v>
       </c>
@@ -10301,7 +10405,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>12</v>
       </c>
@@ -10309,7 +10413,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>13</v>
       </c>
@@ -10317,7 +10421,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>14</v>
       </c>
@@ -10325,7 +10429,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>15</v>
       </c>
@@ -10333,7 +10437,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>16</v>
       </c>
@@ -10341,7 +10445,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>17</v>
       </c>
@@ -10349,7 +10453,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>18</v>
       </c>
@@ -10357,7 +10461,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>19</v>
       </c>
@@ -10365,7 +10469,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>20</v>
       </c>
@@ -10373,7 +10477,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>21</v>
       </c>
@@ -10381,7 +10485,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>22</v>
       </c>
@@ -10389,7 +10493,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>23</v>
       </c>
@@ -10397,7 +10501,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>24</v>
       </c>
@@ -10405,7 +10509,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>25</v>
       </c>
@@ -10413,7 +10517,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>26</v>
       </c>
@@ -10421,7 +10525,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>27</v>
       </c>
@@ -10429,7 +10533,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>28</v>
       </c>
@@ -10437,7 +10541,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>29</v>
       </c>
@@ -10445,7 +10549,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>30</v>
       </c>
@@ -10461,68 +10565,71 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E51963-231E-443F-8008-D46429424FA2}">
-  <dimension ref="A1:Q27"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R27"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.58203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.58203125" customWidth="1"/>
-    <col min="3" max="3" width="12.08203125" customWidth="1"/>
-    <col min="4" max="4" width="11.58203125" customWidth="1"/>
+    <col min="1" max="1" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.625" customWidth="1"/>
+    <col min="4" max="4" width="12.125" customWidth="1"/>
+    <col min="5" max="5" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="L1" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="N1" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="10"/>
+      <c r="P1" s="1"/>
       <c r="Q1" s="10"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R1" s="10"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
         <v>79</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>4</v>
@@ -10560,1212 +10667,1290 @@
       <c r="N2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="10"/>
+      <c r="O2" s="10" t="s">
+        <v>4</v>
+      </c>
       <c r="P2" s="10"/>
       <c r="Q2" s="10"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R2" s="10"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>83</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="F3" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="G3" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="H3" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="I3" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="L3" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="M3" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="N3" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="O3" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="O3" s="10"/>
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R3" s="10"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="11">
         <v>10</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>60</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>5</v>
       </c>
-      <c r="E4">
-        <f>D4</f>
+      <c r="F4">
+        <f>E4</f>
         <v>5</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>25</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>8</v>
       </c>
-      <c r="H4">
-        <f>G4</f>
+      <c r="I4">
+        <f>H4</f>
         <v>8</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>10</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>12</v>
       </c>
-      <c r="K4">
-        <f>J4</f>
+      <c r="L4">
+        <f>K4</f>
         <v>12</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>5</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>15</v>
       </c>
-      <c r="N4">
-        <f>M4</f>
+      <c r="O4">
+        <f>N4</f>
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="11">
         <v>10</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>60</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>5</v>
       </c>
-      <c r="E5">
-        <f t="shared" ref="E5:E27" si="0">D5</f>
+      <c r="F5">
+        <f t="shared" ref="F5:F27" si="0">E5</f>
         <v>5</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>25</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>8</v>
       </c>
-      <c r="H5">
-        <f t="shared" ref="H5:H27" si="1">G5</f>
+      <c r="I5">
+        <f t="shared" ref="I5:I27" si="1">H5</f>
         <v>8</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>10</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>12</v>
       </c>
-      <c r="K5">
-        <f t="shared" ref="K5:K27" si="2">J5</f>
+      <c r="L5">
+        <f t="shared" ref="L5:L27" si="2">K5</f>
         <v>12</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>5</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>15</v>
       </c>
-      <c r="N5">
-        <f t="shared" ref="N5:N27" si="3">M5</f>
+      <c r="O5">
+        <f t="shared" ref="O5:O27" si="3">N5</f>
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="11">
         <v>10</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>60</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>5</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>25</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>8</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>10</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>12</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>5</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>15</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="11">
         <v>10</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>60</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>5</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>25</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>8</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>10</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>12</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>5</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>15</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="11">
         <v>10</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>60</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>5</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>25</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>8</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>10</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>12</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>5</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>15</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="11">
         <v>10</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>60</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>5</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>25</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>8</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>10</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>12</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>5</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>15</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C10" s="11">
         <v>10</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>60</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>5</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>25</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>8</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>10</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>12</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>5</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>15</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C11" s="11">
         <v>10</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>60</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>5</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>25</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>8</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>10</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>12</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>5</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>15</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="11">
         <v>10</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>60</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>5</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>25</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>8</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>10</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>12</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>5</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>15</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="11">
         <v>10</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>60</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>5</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>25</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>8</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>10</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>12</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>5</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>15</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="str">
         <f>"Anti"&amp;A8</f>
         <v>AntiCritRate</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" s="11">
         <v>10</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>60</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>5</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>25</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>8</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>10</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>12</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>5</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>15</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="str">
         <f t="shared" ref="A15:A19" si="4">"Anti"&amp;A9</f>
         <v>AntiCounterRate</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" s="11">
         <v>10</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>60</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>5</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>25</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>8</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>10</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>12</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>5</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>15</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="str">
         <f t="shared" si="4"/>
         <v>AntiComboRate</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" s="11">
         <v>10</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>60</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>5</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>25</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>8</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>10</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>12</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>5</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>15</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="str">
         <f t="shared" si="4"/>
         <v>AntiDodgeRate</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="11">
         <v>10</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>60</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>5</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>25</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>8</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>10</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>12</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>5</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>15</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="str">
         <f t="shared" si="4"/>
         <v>AntiStunRate</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" s="11">
         <v>10</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>60</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>5</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>25</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>8</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>10</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>12</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>5</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>15</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="str">
         <f t="shared" si="4"/>
         <v>AntiLifeStealRate</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" s="11">
         <v>10</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>60</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>5</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>25</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>8</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>10</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>12</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>5</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>15</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" s="11">
         <v>10</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>60</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>5</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>25</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>8</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>10</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>12</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>5</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>15</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="str">
         <f>"Anti"&amp;A20</f>
         <v>AntiCritDmg</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C21" s="11">
         <v>10</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>60</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>5</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>25</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>8</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>10</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>12</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>5</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>15</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" s="11">
         <v>10</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>60</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>5</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>25</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>8</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>10</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>12</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>5</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>15</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C23" s="11">
         <v>10</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>60</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>5</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>25</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>8</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>10</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>12</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>5</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>15</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C24" s="11">
         <v>10</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>60</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>5</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>25</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>8</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>10</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>12</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>5</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>15</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C25" s="11">
         <v>10</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>60</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>5</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>25</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>8</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>10</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>12</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>5</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>15</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C26" s="11">
         <v>10</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>60</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>5</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>25</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>8</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>10</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>12</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>5</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>15</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C27" s="11">
         <v>10</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>60</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>5</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>25</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>8</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>10</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>12</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>5</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>15</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
@@ -11779,17 +11964,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.25" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.08203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.125" style="2" customWidth="1"/>
     <col min="3" max="4" width="10" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.75" style="2" customWidth="1"/>
-    <col min="6" max="16" width="8.6640625" customWidth="1"/>
+    <col min="6" max="16" width="8.625" customWidth="1"/>
     <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="2">
         <v>0</v>
@@ -11799,13 +11984,13 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B2" s="5" t="s">
         <v>29</v>
       </c>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
         <v>38</v>
       </c>
@@ -11813,124 +11998,124 @@
       <c r="D3"/>
       <c r="E3"/>
     </row>
-    <row r="4" spans="1:8" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="B4" s="5" t="s">
         <v>39</v>
       </c>
       <c r="F4" s="2"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B5" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B6" s="6" t="s">
         <v>41</v>
       </c>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B7" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B8" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C8" s="4"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B9" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B10" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B11" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B12" s="7" t="str">
         <f>"Anti"&amp;B6</f>
         <v>AntiCritRate</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B13" s="7" t="str">
         <f t="shared" ref="B13:B17" si="0">"Anti"&amp;B7</f>
         <v>AntiCounterRate</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="str">
         <f t="shared" si="0"/>
         <v>AntiComboRate</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B15" s="7" t="str">
         <f t="shared" si="0"/>
         <v>AntiDodgeRate</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B16" s="7" t="str">
         <f t="shared" si="0"/>
         <v>AntiStunRate</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" s="7" t="str">
         <f t="shared" si="0"/>
         <v>AntiLifeStealRate</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="str">
         <f>"Anti"&amp;B18</f>
         <v>AntiCritDmg</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>53</v>
       </c>

--- a/Assets/Excel/Pets.xlsx
+++ b/Assets/Excel/Pets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A77B198-EB06-48A0-9E7C-2F076C0A44E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FEAA0CE-305B-4052-8510-C7957068E3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pets" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="154">
   <si>
     <t>String</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -597,6 +597,14 @@
   </si>
   <si>
     <t>弱化宠物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽取权重</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GachaWeight</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -994,184 +1002,194 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E113BB45-2004-4A47-8070-A66C92D5B66E}">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.75" style="2" customWidth="1"/>
-    <col min="4" max="4" width="9.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.75" style="2" customWidth="1"/>
-    <col min="13" max="13" width="10.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="2" max="2" width="7.5" style="2" customWidth="1"/>
+    <col min="3" max="4" width="10.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.75" style="2" customWidth="1"/>
+    <col min="14" max="14" width="10.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>101</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="2">
+        <v>50</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="2">
+      <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <v>5</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <v>350</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
       </c>
       <c r="J4" s="2">
         <v>0</v>
@@ -1188,92 +1206,101 @@
       <c r="N4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>102</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="2">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="2">
+      <c r="D5" s="2">
         <v>2</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
         <v>2</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>0</v>
       </c>
-      <c r="I5" s="2">
+      <c r="J5" s="2">
         <v>137</v>
       </c>
-      <c r="J5" s="2">
+      <c r="K5" s="2">
         <v>1</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L5" s="2">
+      <c r="M5" s="2">
         <v>15</v>
-      </c>
-      <c r="M5" s="2">
-        <v>1</v>
       </c>
       <c r="N5" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>103</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="2">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="2">
+      <c r="D6" s="2">
         <v>3</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="2">
         <v>1</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <v>108</v>
       </c>
-      <c r="I6" s="2">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
-      <c r="J6" s="2">
+      <c r="K6" s="2">
         <v>1</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L6" s="2">
+      <c r="M6" s="2">
         <v>10</v>
       </c>
-      <c r="M6" s="2">
+      <c r="N6" s="2">
         <v>5</v>
       </c>
-      <c r="N6" s="2">
+      <c r="O6" s="2">
         <v>999</v>
       </c>
     </row>
@@ -1287,7 +1314,7 @@
           <x14:formula1>
             <xm:f>备份!$B$1:$B$25</xm:f>
           </x14:formula1>
-          <xm:sqref>K4:K6</xm:sqref>
+          <xm:sqref>L4:L6</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
